--- a/data/bist_screener_2026-05-07.xlsx
+++ b/data/bist_screener_2026-05-07.xlsx
@@ -3109,42 +3109,44 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>4.45</v>
+        <v>100</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>0.0723</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>8820000</v>
+        <v>28810000</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.5366</v>
+        <v>0.654</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>71.20999999999999</v>
-      </c>
-      <c r="G61" s="6" t="inlineStr"/>
+        <v>55.61</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>28.57</v>
+      </c>
       <c r="H61" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>-0.2148</v>
+        <v>0.0218</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>-1.5579</v>
+        <v>-0.9307</v>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr"/>
@@ -3152,42 +3154,42 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AVPGY</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>63</v>
+        <v>4.45</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.0211</v>
+        <v>0.0723</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>1210000</v>
+        <v>8820000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.2632</v>
+        <v>0.5366</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>75.44</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>12.78</v>
-      </c>
+        <v>71.20999999999999</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr"/>
+        <v>-0.2148</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>-1.5579</v>
+      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
@@ -3195,42 +3197,42 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>BUCIM</t>
+          <t>AVPGY</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>6.36</v>
+        <v>63</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>0.0176</v>
+        <v>0.0211</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>8530000</v>
+        <v>1210000</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.454</v>
+        <v>0.2632</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>57.83</v>
-      </c>
-      <c r="G63" s="6" t="inlineStr"/>
+        <v>75.44</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>12.78</v>
+      </c>
       <c r="H63" s="7" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>-0.0537</v>
-      </c>
-      <c r="J63" s="8" t="n">
-        <v>-4.4859</v>
-      </c>
+        <v>0.0496</v>
+      </c>
+      <c r="J63" s="6" t="inlineStr"/>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr"/>
@@ -3238,33 +3240,33 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KOCMT</t>
+          <t>BUCIM</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>2.72</v>
+        <v>6.36</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.0149</v>
+        <v>0.0176</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>24990000</v>
+        <v>8530000</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.2582</v>
+        <v>0.454</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>62.52</v>
+        <v>57.83</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="n">
         <v>0.57</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>-0.0862</v>
+        <v>-0.0537</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>-114.5083</v>
+        <v>-4.4859</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -3273,7 +3275,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST BURSA</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
@@ -3281,44 +3283,42 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>MHRGY</t>
+          <t>KOCMT</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>3.87</v>
+        <v>2.72</v>
       </c>
       <c r="C65" s="8" t="n">
-        <v>0.0211</v>
+        <v>0.0149</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>5660000</v>
+        <v>24990000</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.2243</v>
+        <v>0.2582</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>61.54</v>
-      </c>
-      <c r="G65" s="7" t="n">
-        <v>9.539999999999999</v>
-      </c>
+        <v>62.52</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr"/>
       <c r="H65" s="7" t="n">
         <v>0.57</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.0692</v>
+        <v>-0.0862</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>14.2382</v>
+        <v>-114.5083</v>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
@@ -3326,42 +3326,44 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AYEN</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>35.78</v>
+        <v>3.87</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.0073</v>
+        <v>0.0211</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>3540000</v>
+        <v>5660000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.1697</v>
+        <v>0.2243</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>57.23</v>
+        <v>61.54</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>46.21</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.57</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.0143</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
+        <v>0.0692</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>14.2382</v>
+      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KAYSERİ, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
@@ -3369,40 +3371,42 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>TSPOR</t>
+          <t>AYEN</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>1.01</v>
+        <v>35.78</v>
       </c>
       <c r="C67" s="8" t="n">
-        <v>0.01</v>
+        <v>0.0073</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>288700000</v>
+        <v>3540000</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.49</v>
+        <v>0.1697</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="G67" s="6" t="inlineStr"/>
+        <v>57.23</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>46.21</v>
+      </c>
       <c r="H67" s="7" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>-0.1067</v>
+        <v>0.0143</v>
       </c>
       <c r="J67" s="6" t="inlineStr"/>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST YILDIZ</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KAYSERİ, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr"/>
@@ -3410,44 +3414,40 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>TSPOR</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>28810000</v>
+        <v>288700000</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.654</v>
+        <v>0.49</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>51.52</v>
-      </c>
+        <v>54.08</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="3" t="n">
         <v>0.58</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.0128</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>5.750299999999999</v>
-      </c>
+        <v>-0.1067</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
@@ -7230,44 +7230,44 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>YUNSA</t>
+          <t>VAKBN</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>8.630000000000001</v>
+        <v>32.06</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>0.0311</v>
+        <v>0.0191</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>6360000</v>
+        <v>47400000</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>0.4212</v>
+        <v>0.0793</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>52.66</v>
+        <v>46.04</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>11.28</v>
+        <v>4.39</v>
       </c>
       <c r="H156" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>0.0941</v>
+        <v>0.2493</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>-0.5928</v>
+        <v>-0.4081</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST TEKİRDAĞ</t>
+          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr"/>
@@ -7275,33 +7275,35 @@
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>PETKM</t>
+          <t>YUNSA</t>
         </is>
       </c>
       <c r="B157" s="7" t="n">
-        <v>23.76</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="C157" s="8" t="n">
-        <v>-0.0149</v>
+        <v>0.0311</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>81340000</v>
+        <v>6360000</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>0.49</v>
+        <v>0.4212</v>
       </c>
       <c r="F157" s="7" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="G157" s="6" t="inlineStr"/>
+        <v>52.66</v>
+      </c>
+      <c r="G157" s="7" t="n">
+        <v>11.28</v>
+      </c>
       <c r="H157" s="7" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I157" s="8" t="n">
-        <v>-0.1607</v>
+        <v>0.0941</v>
       </c>
       <c r="J157" s="8" t="n">
-        <v>-3.4952</v>
+        <v>-0.5928</v>
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
@@ -7310,7 +7312,7 @@
       </c>
       <c r="L157" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST İZMİR, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M157" s="6" t="inlineStr"/>
@@ -7318,44 +7320,42 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>KIMMR</t>
+          <t>PETKM</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>17.29</v>
+        <v>23.76</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>0.0441</v>
+        <v>-0.0149</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>3390000</v>
+        <v>81340000</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>0.2708</v>
+        <v>0.49</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="G158" s="3" t="n">
-        <v>6.55</v>
-      </c>
+        <v>61.4</v>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>0.1738</v>
+        <v>-0.1607</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>2.5571</v>
+        <v>-3.4952</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST İZMİR, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr"/>
@@ -7363,42 +7363,44 @@
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>KIMMR</t>
         </is>
       </c>
       <c r="B159" s="7" t="n">
-        <v>5.11</v>
+        <v>17.29</v>
       </c>
       <c r="C159" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0441</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>199410000</v>
+        <v>3390000</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>0.4953</v>
+        <v>0.2708</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>46.14</v>
+        <v>49.1</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>24.04</v>
+        <v>6.55</v>
       </c>
       <c r="H159" s="7" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="J159" s="6" t="inlineStr"/>
+        <v>0.1738</v>
+      </c>
+      <c r="J159" s="8" t="n">
+        <v>2.5571</v>
+      </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr"/>
@@ -7406,42 +7408,42 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>KTSKR</t>
+          <t>EUREN</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>117.6</v>
+        <v>5.11</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>-0.0408</v>
+        <v>0.002</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>1770000</v>
+        <v>199410000</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>0.3086</v>
+        <v>0.4953</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
+        <v>46.14</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>24.04</v>
+      </c>
       <c r="H160" s="3" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="J160" s="4" t="n">
-        <v>-4.305400000000001</v>
-      </c>
+        <v>0.0452</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr"/>
@@ -7449,42 +7451,42 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>KTSKR</t>
         </is>
       </c>
       <c r="B161" s="7" t="n">
-        <v>120.1</v>
+        <v>117.6</v>
       </c>
       <c r="C161" s="8" t="n">
-        <v>-0.0066</v>
+        <v>-0.0408</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2390000</v>
+        <v>1770000</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>0.3279</v>
+        <v>0.3086</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="G161" s="7" t="n">
-        <v>2.25</v>
-      </c>
+        <v>54.73</v>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
       <c r="H161" s="7" t="n">
         <v>0.95</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>0.5731000000000001</v>
-      </c>
-      <c r="J161" s="6" t="inlineStr"/>
+        <v>-0.019</v>
+      </c>
+      <c r="J161" s="8" t="n">
+        <v>-4.305400000000001</v>
+      </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M161" s="6" t="inlineStr"/>
@@ -7492,44 +7494,44 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>VAKBN</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>32.06</v>
+        <v>66.2</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>0.0191</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>47400000</v>
+        <v>15560000</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>0.0793</v>
+        <v>0.1332</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>46.04</v>
+        <v>60.54</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>4.12</v>
+        <v>8.51</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>0.2783</v>
+        <v>0.1332</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>1.0588</v>
+        <v>5.345599999999999</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST ANKARA, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr"/>
@@ -7537,40 +7539,42 @@
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>CELHA</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="B163" s="7" t="n">
-        <v>13.89</v>
+        <v>120.1</v>
       </c>
       <c r="C163" s="8" t="n">
-        <v>0.0036</v>
+        <v>-0.0066</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>17050000</v>
+        <v>2390000</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>0.4024</v>
+        <v>0.3279</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>76.67</v>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
+        <v>47.43</v>
+      </c>
+      <c r="G163" s="7" t="n">
+        <v>2.25</v>
+      </c>
       <c r="H163" s="7" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.1674</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J163" s="6" t="inlineStr"/>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M163" s="6" t="inlineStr"/>
@@ -7578,42 +7582,40 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>MTRYO</t>
+          <t>CELHA</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>10.54</v>
+        <v>13.89</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>-0.0168</v>
+        <v>0.0036</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>611760</v>
+        <v>17050000</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>0.7481</v>
+        <v>0.4024</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>62.04</v>
+        <v>76.67</v>
       </c>
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="3" t="n">
         <v>0.98</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-0.0451</v>
-      </c>
-      <c r="J164" s="4" t="n">
-        <v>-5.186900000000001</v>
-      </c>
+        <v>-0.1674</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr"/>
@@ -7621,42 +7623,42 @@
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>KRVGD</t>
+          <t>MTRYO</t>
         </is>
       </c>
       <c r="B165" s="7" t="n">
-        <v>3.1</v>
+        <v>10.54</v>
       </c>
       <c r="C165" s="8" t="n">
-        <v>0.0032</v>
+        <v>-0.0168</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>14370000</v>
+        <v>611760</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>0.392</v>
+        <v>0.7481</v>
       </c>
       <c r="F165" s="7" t="n">
-        <v>62.71</v>
+        <v>62.04</v>
       </c>
       <c r="G165" s="6" t="inlineStr"/>
       <c r="H165" s="7" t="n">
         <v>0.98</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.0102</v>
+        <v>-0.0451</v>
       </c>
       <c r="J165" s="8" t="n">
-        <v>1.099</v>
+        <v>-5.186900000000001</v>
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M165" s="6" t="inlineStr"/>
@@ -7664,44 +7666,42 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>KRVGD</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.0032</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>7340000</v>
+        <v>14370000</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>0.1877</v>
+        <v>0.392</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="G166" s="3" t="n">
-        <v>32.35</v>
-      </c>
+        <v>62.71</v>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="3" t="n">
         <v>0.98</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>0.035</v>
+        <v>-0.0102</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>-1.9718</v>
+        <v>1.099</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr"/>
@@ -7709,42 +7709,44 @@
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>REEDR</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B167" s="7" t="n">
-        <v>8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="C167" s="8" t="n">
-        <v>0.0336</v>
+        <v>0.0192</v>
       </c>
       <c r="D167" s="9" t="n">
-        <v>33810000</v>
+        <v>7340000</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>0.3803</v>
+        <v>0.1877</v>
       </c>
       <c r="F167" s="7" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="G167" s="6" t="inlineStr"/>
+        <v>36.35</v>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>32.35</v>
+      </c>
       <c r="H167" s="7" t="n">
         <v>0.98</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.1566</v>
+        <v>0.035</v>
       </c>
       <c r="J167" s="8" t="n">
-        <v>0.7471</v>
+        <v>-1.9718</v>
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M167" s="6" t="inlineStr"/>
@@ -7752,40 +7754,42 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>BORSK</t>
+          <t>REEDR</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>7.28</v>
+        <v>8</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>-0.0136</v>
+        <v>0.0336</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>16590000</v>
+        <v>33810000</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>0.6457999999999999</v>
+        <v>0.3803</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>54.16</v>
+        <v>56.69</v>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="3" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>-0.0042</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr"/>
+        <v>-0.1566</v>
+      </c>
+      <c r="J168" s="4" t="n">
+        <v>0.7471</v>
+      </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr"/>
@@ -7793,44 +7797,40 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>BORSK</t>
         </is>
       </c>
       <c r="B169" s="7" t="n">
-        <v>118.6</v>
+        <v>7.28</v>
       </c>
       <c r="C169" s="8" t="n">
-        <v>0.0076</v>
+        <v>-0.0136</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>18130000</v>
+        <v>16590000</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>0.4894</v>
+        <v>0.6457999999999999</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>59.73</v>
-      </c>
-      <c r="G169" s="7" t="n">
-        <v>15.33</v>
-      </c>
+        <v>54.16</v>
+      </c>
+      <c r="G169" s="6" t="inlineStr"/>
       <c r="H169" s="7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>0.07629999999999999</v>
-      </c>
-      <c r="J169" s="8" t="n">
-        <v>-0.2259</v>
-      </c>
+        <v>-0.0042</v>
+      </c>
+      <c r="J169" s="6" t="inlineStr"/>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M169" s="6" t="inlineStr"/>
@@ -7838,44 +7838,44 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>IDGYO</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>3.35</v>
+        <v>118.6</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>0.0152</v>
+        <v>0.0076</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>2410000</v>
+        <v>18130000</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>0.2502</v>
+        <v>0.4894</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>37.57</v>
+        <v>59.73</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>7.96</v>
+        <v>15.33</v>
       </c>
       <c r="H170" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>0.1599</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>-1.0243</v>
+        <v>-0.2259</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr"/>
@@ -7883,42 +7883,44 @@
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>IDGYO</t>
         </is>
       </c>
       <c r="B171" s="7" t="n">
-        <v>1.2</v>
+        <v>3.35</v>
       </c>
       <c r="C171" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.0152</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>350630000</v>
+        <v>2410000</v>
       </c>
       <c r="E171" s="8" t="n">
-        <v>0.3999</v>
+        <v>0.2502</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>61.99</v>
-      </c>
-      <c r="G171" s="6" t="inlineStr"/>
+        <v>37.57</v>
+      </c>
+      <c r="G171" s="7" t="n">
+        <v>7.96</v>
+      </c>
       <c r="H171" s="7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>-0.0873</v>
+        <v>0.1599</v>
       </c>
       <c r="J171" s="8" t="n">
-        <v>-1.5758</v>
+        <v>-1.0243</v>
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM</t>
         </is>
       </c>
       <c r="M171" s="6" t="inlineStr"/>
@@ -7926,42 +7928,42 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>20.54</v>
+        <v>1.2</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>0.026</v>
+        <v>0.0256</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>42540000</v>
+        <v>350630000</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>0.3295</v>
+        <v>0.3999</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="G172" s="3" t="n">
-        <v>13.99</v>
-      </c>
+        <v>61.99</v>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="3" t="n">
         <v>1.02</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>0.0837</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
+        <v>-0.0873</v>
+      </c>
+      <c r="J172" s="4" t="n">
+        <v>-1.5758</v>
+      </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 50, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr"/>
@@ -7969,42 +7971,42 @@
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>AGROT</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B173" s="7" t="n">
-        <v>3.15</v>
+        <v>20.54</v>
       </c>
       <c r="C173" s="8" t="n">
-        <v>0.0261</v>
+        <v>0.026</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>105870000</v>
+        <v>42540000</v>
       </c>
       <c r="E173" s="8" t="n">
-        <v>0.3517</v>
+        <v>0.3295</v>
       </c>
       <c r="F173" s="7" t="n">
-        <v>52.13</v>
-      </c>
-      <c r="G173" s="6" t="inlineStr"/>
+        <v>67.23</v>
+      </c>
+      <c r="G173" s="7" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H173" s="7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.0902</v>
-      </c>
-      <c r="J173" s="8" t="n">
-        <v>-0.5942000000000001</v>
-      </c>
+        <v>0.0837</v>
+      </c>
+      <c r="J173" s="6" t="inlineStr"/>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 50, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M173" s="6" t="inlineStr"/>
@@ -8012,42 +8014,42 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>AGROT</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>115</v>
+        <v>3.15</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>0.0132</v>
+        <v>0.0261</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>2970000</v>
+        <v>105870000</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>0.1496</v>
+        <v>0.3517</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>51.94</v>
+        <v>52.13</v>
       </c>
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-0.1125</v>
+        <v>-0.0902</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>0.0537</v>
+        <v>-0.5942000000000001</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr"/>
@@ -8055,44 +8057,42 @@
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B175" s="7" t="n">
-        <v>265</v>
+        <v>115</v>
       </c>
       <c r="C175" s="8" t="n">
-        <v>0.0173</v>
+        <v>0.0132</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>66350</v>
+        <v>2970000</v>
       </c>
       <c r="E175" s="8" t="n">
-        <v>0.3301</v>
+        <v>0.1496</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="G175" s="7" t="n">
-        <v>15.3</v>
-      </c>
+        <v>51.94</v>
+      </c>
+      <c r="G175" s="6" t="inlineStr"/>
       <c r="H175" s="7" t="n">
         <v>1.03</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>0.07629999999999999</v>
+        <v>-0.1125</v>
       </c>
       <c r="J175" s="8" t="n">
-        <v>2.0964</v>
+        <v>0.0537</v>
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST TEMETTU, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M175" s="6" t="inlineStr"/>
@@ -8100,42 +8100,44 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SELVA</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>2.5</v>
+        <v>265</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>0</v>
+        <v>0.0173</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>175100000</v>
+        <v>66350</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>0.6808</v>
+        <v>0.3301</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>53.57</v>
-      </c>
-      <c r="G176" s="2" t="inlineStr"/>
+        <v>46.6</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>15.3</v>
+      </c>
       <c r="H176" s="3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>-0.2143</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>-4.419</v>
+        <v>2.0964</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST TEMETTU, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr"/>
@@ -8143,44 +8145,42 @@
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>AKFIS</t>
+          <t>SELVA</t>
         </is>
       </c>
       <c r="B177" s="7" t="n">
-        <v>53</v>
+        <v>2.5</v>
       </c>
       <c r="C177" s="8" t="n">
-        <v>-0.0311</v>
+        <v>0</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>5200000</v>
+        <v>175100000</v>
       </c>
       <c r="E177" s="8" t="n">
-        <v>0.15</v>
+        <v>0.6808</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="G177" s="7" t="n">
-        <v>20.12</v>
-      </c>
+        <v>53.57</v>
+      </c>
+      <c r="G177" s="6" t="inlineStr"/>
       <c r="H177" s="7" t="n">
         <v>1.05</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>0.0636</v>
+        <v>-0.2143</v>
       </c>
       <c r="J177" s="8" t="n">
-        <v>156.1426</v>
+        <v>-4.419</v>
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST KONYA</t>
         </is>
       </c>
       <c r="M177" s="6" t="inlineStr"/>
@@ -8188,42 +8188,44 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>EYGYO</t>
+          <t>AKFIS</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>2.77</v>
+        <v>53</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>0.0073</v>
+        <v>-0.0311</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>15910000</v>
+        <v>5200000</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>0.3551</v>
+        <v>0.15</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>43.16</v>
-      </c>
-      <c r="G178" s="2" t="inlineStr"/>
+        <v>58.67</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>20.12</v>
+      </c>
       <c r="H178" s="3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>-0.3417</v>
+        <v>0.0636</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>-2.1476</v>
+        <v>156.1426</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr"/>
@@ -8231,42 +8233,42 @@
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>ATAKP</t>
+          <t>EYGYO</t>
         </is>
       </c>
       <c r="B179" s="7" t="n">
-        <v>52.35</v>
+        <v>2.77</v>
       </c>
       <c r="C179" s="8" t="n">
-        <v>0.0048</v>
+        <v>0.0073</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>681320</v>
+        <v>15910000</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>0.2034</v>
+        <v>0.3551</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>49.21</v>
+        <v>43.16</v>
       </c>
       <c r="G179" s="6" t="inlineStr"/>
       <c r="H179" s="7" t="n">
         <v>1.06</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.0317</v>
+        <v>-0.3417</v>
       </c>
       <c r="J179" s="8" t="n">
-        <v>0.1112</v>
+        <v>-2.1476</v>
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M179" s="6" t="inlineStr"/>
@@ -8274,42 +8276,42 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>ATAKP</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>3.89</v>
+        <v>52.35</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>0.0571</v>
+        <v>0.0048</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>209630000</v>
+        <v>681320</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.2034</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>56.83</v>
+        <v>49.21</v>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>-0.131</v>
+        <v>-0.0317</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>-4.6418</v>
+        <v>0.1112</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST AYDIN, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr"/>
@@ -8317,81 +8319,83 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>KERVN</t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="B181" s="7" t="n">
-        <v>4.5</v>
+        <v>91.7</v>
       </c>
       <c r="C181" s="8" t="n">
-        <v>0.0689</v>
+        <v>0.0438</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>781930</v>
+        <v>311540</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>0.3049</v>
+        <v>0.1275</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>60.91</v>
+        <v>63.86</v>
       </c>
       <c r="G181" s="6" t="inlineStr"/>
       <c r="H181" s="7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I181" s="8" t="n">
-        <v>-0.0213</v>
+        <v>-0.0189</v>
       </c>
       <c r="J181" s="6" t="inlineStr"/>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
-        </is>
-      </c>
-      <c r="L181" s="6" t="inlineStr"/>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
+      <c r="L181" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+        </is>
+      </c>
       <c r="M181" s="6" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.0571</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>124700000</v>
+        <v>209630000</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>0.7881999999999999</v>
+        <v>0.3512</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="G182" s="3" t="n">
-        <v>23.16</v>
-      </c>
+        <v>56.83</v>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>0.1155</v>
+        <v>-0.131</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>0.1014</v>
+        <v>-4.6418</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST AYDIN, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr"/>
@@ -8399,80 +8403,72 @@
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>KERVN</t>
         </is>
       </c>
       <c r="B183" s="7" t="n">
-        <v>66.2</v>
+        <v>4.5</v>
       </c>
       <c r="C183" s="8" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0689</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>15560000</v>
+        <v>781930</v>
       </c>
       <c r="E183" s="8" t="n">
-        <v>0.1332</v>
+        <v>0.3049</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>60.54</v>
-      </c>
-      <c r="G183" s="7" t="n">
-        <v>10.58</v>
-      </c>
+        <v>60.91</v>
+      </c>
+      <c r="G183" s="6" t="inlineStr"/>
       <c r="H183" s="7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>0.1222</v>
-      </c>
-      <c r="J183" s="8" t="n">
-        <v>-0.8391</v>
-      </c>
+        <v>-0.0213</v>
+      </c>
+      <c r="J183" s="6" t="inlineStr"/>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>İletişim</t>
-        </is>
-      </c>
-      <c r="L183" s="6" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST ANKARA, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
-        </is>
-      </c>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
+      <c r="L183" s="6" t="inlineStr"/>
       <c r="M183" s="6" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ISFIN</t>
+          <t>HDFGS</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>20.5</v>
+        <v>3.58</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>0.0039</v>
+        <v>0.0347</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>2620000</v>
+        <v>124700000</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>0.4001</v>
+        <v>0.7881999999999999</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>55.01</v>
+        <v>56</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>3.75</v>
+        <v>23.16</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>0.3434</v>
+        <v>0.1155</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>-0.273</v>
+        <v>0.1014</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -8481,7 +8477,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr"/>
@@ -8489,42 +8485,44 @@
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>MERKO</t>
+          <t>ISFIN</t>
         </is>
       </c>
       <c r="B185" s="7" t="n">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="C185" s="8" t="n">
-        <v>0.0638</v>
+        <v>0.0039</v>
       </c>
       <c r="D185" s="9" t="n">
-        <v>135290000</v>
+        <v>2620000</v>
       </c>
       <c r="E185" s="8" t="n">
-        <v>0.851</v>
+        <v>0.4001</v>
       </c>
       <c r="F185" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>55.01</v>
       </c>
       <c r="G185" s="7" t="n">
-        <v>4.79</v>
+        <v>3.75</v>
       </c>
       <c r="H185" s="7" t="n">
         <v>1.09</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>0.2405</v>
-      </c>
-      <c r="J185" s="6" t="inlineStr"/>
+        <v>0.3434</v>
+      </c>
+      <c r="J185" s="8" t="n">
+        <v>-0.273</v>
+      </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M185" s="6" t="inlineStr"/>
@@ -8532,44 +8530,42 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>MERKO</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0638</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>5830000</v>
+        <v>135290000</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>0.501</v>
+        <v>0.851</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>7.43</v>
+        <v>4.79</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0.1769</v>
-      </c>
-      <c r="J186" s="4" t="n">
-        <v>1.394</v>
-      </c>
+        <v>0.2405</v>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST BALIKESİR</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr"/>
@@ -8577,44 +8573,44 @@
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>GWIND</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B187" s="7" t="n">
-        <v>29.06</v>
+        <v>7</v>
       </c>
       <c r="C187" s="8" t="n">
-        <v>0.0196</v>
+        <v>0.0204</v>
       </c>
       <c r="D187" s="9" t="n">
-        <v>38280000</v>
+        <v>5830000</v>
       </c>
       <c r="E187" s="8" t="n">
-        <v>0.3</v>
+        <v>0.501</v>
       </c>
       <c r="F187" s="7" t="n">
-        <v>55.07</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="G187" s="7" t="n">
-        <v>19.46</v>
+        <v>7.43</v>
       </c>
       <c r="H187" s="7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.1769</v>
       </c>
       <c r="J187" s="8" t="n">
-        <v>-0.6212</v>
+        <v>1.394</v>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BALIKESİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M187" s="6" t="inlineStr"/>
@@ -8622,44 +8618,44 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ULKER</t>
+          <t>GWIND</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>130.3</v>
+        <v>29.06</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0196</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>7040000</v>
+        <v>38280000</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>0.5277000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>68.7</v>
+        <v>55.07</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>10.73</v>
+        <v>19.46</v>
       </c>
       <c r="H188" s="3" t="n">
         <v>1.11</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>-0.7368000000000001</v>
+        <v>-0.6212</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 50, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST 50-30, BIST ANKARA, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr"/>
@@ -8667,44 +8663,44 @@
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>ULUFA</t>
+          <t>ULKER</t>
         </is>
       </c>
       <c r="B189" s="7" t="n">
-        <v>4.13</v>
+        <v>130.3</v>
       </c>
       <c r="C189" s="8" t="n">
-        <v>0.0098</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="D189" s="9" t="n">
-        <v>26620000</v>
+        <v>7040000</v>
       </c>
       <c r="E189" s="8" t="n">
-        <v>0.2096</v>
+        <v>0.5277000000000001</v>
       </c>
       <c r="F189" s="7" t="n">
-        <v>40.91</v>
+        <v>68.7</v>
       </c>
       <c r="G189" s="7" t="n">
-        <v>2.97</v>
+        <v>10.73</v>
       </c>
       <c r="H189" s="7" t="n">
         <v>1.11</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>0.3985</v>
+        <v>0.1202</v>
       </c>
       <c r="J189" s="8" t="n">
-        <v>-0.6119</v>
+        <v>-0.7368000000000001</v>
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 50, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST 50-30, BIST ANKARA, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M189" s="6" t="inlineStr"/>
@@ -8712,42 +8708,44 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>IMASM</t>
+          <t>ULUFA</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>3.67</v>
+        <v>4.13</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>-0.0317</v>
+        <v>0.0098</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>37240000</v>
+        <v>26620000</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>0.6734</v>
+        <v>0.2096</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="G190" s="2" t="inlineStr"/>
+        <v>40.91</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>2.97</v>
+      </c>
       <c r="H190" s="3" t="n">
         <v>1.11</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>-0.235</v>
+        <v>0.3985</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>-4.909800000000001</v>
+        <v>-0.6119</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr"/>
@@ -8755,44 +8753,42 @@
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>BRKSN</t>
+          <t>IMASM</t>
         </is>
       </c>
       <c r="B191" s="7" t="n">
-        <v>9.449999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="C191" s="8" t="n">
-        <v>0.0283</v>
+        <v>-0.0317</v>
       </c>
       <c r="D191" s="9" t="n">
-        <v>861710</v>
+        <v>37240000</v>
       </c>
       <c r="E191" s="8" t="n">
-        <v>0.7524</v>
+        <v>0.6734</v>
       </c>
       <c r="F191" s="7" t="n">
-        <v>66.56999999999999</v>
-      </c>
-      <c r="G191" s="7" t="n">
-        <v>36.26</v>
-      </c>
+        <v>42.47</v>
+      </c>
+      <c r="G191" s="6" t="inlineStr"/>
       <c r="H191" s="7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I191" s="8" t="n">
-        <v>0.0253</v>
+        <v>-0.235</v>
       </c>
       <c r="J191" s="8" t="n">
-        <v>2.3941</v>
+        <v>-4.909800000000001</v>
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KONYA</t>
         </is>
       </c>
       <c r="M191" s="6" t="inlineStr"/>
@@ -8800,42 +8796,44 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>YIGIT</t>
+          <t>BRKSN</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>25.94</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>0.0528</v>
+        <v>0.0283</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>5460000</v>
+        <v>861710</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>0.2496</v>
+        <v>0.7524</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>63.98</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>39.77</v>
+        <v>36.26</v>
       </c>
       <c r="H192" s="3" t="n">
         <v>1.12</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>0.0323</v>
-      </c>
-      <c r="J192" s="2" t="inlineStr"/>
+        <v>0.0253</v>
+      </c>
+      <c r="J192" s="4" t="n">
+        <v>2.3941</v>
+      </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr"/>
@@ -8843,42 +8841,42 @@
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>CEMAS</t>
+          <t>YIGIT</t>
         </is>
       </c>
       <c r="B193" s="7" t="n">
-        <v>4.99</v>
+        <v>25.94</v>
       </c>
       <c r="C193" s="8" t="n">
-        <v>0.0374</v>
+        <v>0.0528</v>
       </c>
       <c r="D193" s="9" t="n">
-        <v>17150000</v>
+        <v>5460000</v>
       </c>
       <c r="E193" s="8" t="n">
-        <v>0.7140000000000001</v>
+        <v>0.2496</v>
       </c>
       <c r="F193" s="7" t="n">
-        <v>53.13</v>
-      </c>
-      <c r="G193" s="6" t="inlineStr"/>
+        <v>63.98</v>
+      </c>
+      <c r="G193" s="7" t="n">
+        <v>39.77</v>
+      </c>
       <c r="H193" s="7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.3776</v>
-      </c>
-      <c r="J193" s="8" t="n">
-        <v>-5.3326</v>
-      </c>
+        <v>0.0323</v>
+      </c>
+      <c r="J193" s="6" t="inlineStr"/>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M193" s="6" t="inlineStr"/>
@@ -8886,44 +8884,42 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>AKYHO</t>
+          <t>CEMAS</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>2.78</v>
+        <v>4.99</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>0.0036</v>
+        <v>0.0374</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>3010000</v>
+        <v>17150000</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>0.9801000000000001</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="G194" s="5" t="n">
-        <v>6950</v>
-      </c>
+        <v>53.13</v>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="3" t="n">
         <v>1.13</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>0.0002</v>
+        <v>-0.3776</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>-2.3862</v>
+        <v>-5.3326</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr"/>
@@ -8931,42 +8927,44 @@
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>AVOD</t>
+          <t>AKYHO</t>
         </is>
       </c>
       <c r="B195" s="7" t="n">
-        <v>5.15</v>
+        <v>2.78</v>
       </c>
       <c r="C195" s="8" t="n">
-        <v>0.0218</v>
+        <v>0.0036</v>
       </c>
       <c r="D195" s="9" t="n">
-        <v>36470000</v>
+        <v>3010000</v>
       </c>
       <c r="E195" s="8" t="n">
-        <v>0.9287000000000001</v>
+        <v>0.9801000000000001</v>
       </c>
       <c r="F195" s="7" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="G195" s="6" t="inlineStr"/>
+        <v>54.76</v>
+      </c>
+      <c r="G195" s="9" t="n">
+        <v>6950</v>
+      </c>
       <c r="H195" s="7" t="n">
         <v>1.13</v>
       </c>
       <c r="I195" s="8" t="n">
-        <v>-0.1373</v>
+        <v>0.0002</v>
       </c>
       <c r="J195" s="8" t="n">
-        <v>0.8694</v>
+        <v>-2.3862</v>
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL</t>
         </is>
       </c>
       <c r="M195" s="6" t="inlineStr"/>
@@ -8974,42 +8972,42 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>BOBET</t>
+          <t>AVOD</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>20.2</v>
+        <v>5.15</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.0218</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>3450000</v>
+        <v>36470000</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>0.3</v>
+        <v>0.9287000000000001</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>55.1</v>
+        <v>66.12</v>
       </c>
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-0.1716</v>
+        <v>-0.1373</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>-2.2777</v>
+        <v>0.8694</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr"/>
@@ -9017,42 +9015,42 @@
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>DENGE</t>
+          <t>BOBET</t>
         </is>
       </c>
       <c r="B197" s="7" t="n">
-        <v>2.63</v>
+        <v>20.2</v>
       </c>
       <c r="C197" s="8" t="n">
         <v>0.0233</v>
       </c>
       <c r="D197" s="9" t="n">
-        <v>20990000</v>
+        <v>3450000</v>
       </c>
       <c r="E197" s="8" t="n">
-        <v>0.4703</v>
+        <v>0.3</v>
       </c>
       <c r="F197" s="7" t="n">
-        <v>57.36</v>
+        <v>55.1</v>
       </c>
       <c r="G197" s="6" t="inlineStr"/>
       <c r="H197" s="7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I197" s="8" t="n">
-        <v>-0.3344</v>
+        <v>-0.1716</v>
       </c>
       <c r="J197" s="8" t="n">
-        <v>0.7206999999999999</v>
+        <v>-2.2777</v>
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M197" s="6" t="inlineStr"/>
@@ -9060,42 +9058,42 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>SAMAT</t>
+          <t>DENGE</t>
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>5.72</v>
+        <v>2.63</v>
       </c>
       <c r="C198" s="4" t="n">
-        <v>0.0178</v>
+        <v>0.0233</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>2380000</v>
+        <v>20990000</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>0.2951</v>
+        <v>0.4703</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="G198" s="3" t="n">
-        <v>35.48</v>
-      </c>
+        <v>57.36</v>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="3" t="n">
         <v>1.15</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="J198" s="2" t="inlineStr"/>
+        <v>-0.3344</v>
+      </c>
+      <c r="J198" s="4" t="n">
+        <v>0.7206999999999999</v>
+      </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr"/>
@@ -9103,44 +9101,42 @@
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>SAMAT</t>
         </is>
       </c>
       <c r="B199" s="7" t="n">
-        <v>56.1</v>
+        <v>5.72</v>
       </c>
       <c r="C199" s="8" t="n">
-        <v>0.0585</v>
+        <v>0.0178</v>
       </c>
       <c r="D199" s="9" t="n">
-        <v>7810000</v>
+        <v>2380000</v>
       </c>
       <c r="E199" s="8" t="n">
-        <v>0.0513</v>
+        <v>0.2951</v>
       </c>
       <c r="F199" s="7" t="n">
-        <v>80.87</v>
+        <v>55.66</v>
       </c>
       <c r="G199" s="7" t="n">
-        <v>24.7</v>
+        <v>35.48</v>
       </c>
       <c r="H199" s="7" t="n">
         <v>1.15</v>
       </c>
       <c r="I199" s="8" t="n">
-        <v>0.04940000000000001</v>
-      </c>
-      <c r="J199" s="8" t="n">
-        <v>0.0143</v>
-      </c>
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="J199" s="6" t="inlineStr"/>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST ANKARA</t>
         </is>
       </c>
       <c r="M199" s="6" t="inlineStr"/>
@@ -9148,44 +9144,44 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CONSE</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>3.45</v>
+        <v>56.1</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>0.0177</v>
+        <v>0.0585</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>23870000</v>
+        <v>7810000</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>0.4901</v>
+        <v>0.0513</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>53.3</v>
+        <v>80.87</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>23.58</v>
+        <v>24.7</v>
       </c>
       <c r="H200" s="3" t="n">
         <v>1.15</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>0.0546</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="J200" s="4" t="n">
-        <v>-0.8634000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr"/>
@@ -9193,44 +9189,44 @@
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>CONSE</t>
         </is>
       </c>
       <c r="B201" s="7" t="n">
-        <v>10.49</v>
+        <v>3.45</v>
       </c>
       <c r="C201" s="8" t="n">
-        <v>0.09960000000000001</v>
-      </c>
-      <c r="D201" s="7" t="n">
-        <v>16120000</v>
+        <v>0.0177</v>
+      </c>
+      <c r="D201" s="9" t="n">
+        <v>23870000</v>
       </c>
       <c r="E201" s="8" t="n">
-        <v>0.9556</v>
+        <v>0.4901</v>
       </c>
       <c r="F201" s="7" t="n">
-        <v>67.11</v>
+        <v>53.3</v>
       </c>
       <c r="G201" s="7" t="n">
-        <v>7.13</v>
+        <v>23.58</v>
       </c>
       <c r="H201" s="7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="I201" s="8" t="n">
-        <v>0.2011</v>
+        <v>0.0546</v>
       </c>
       <c r="J201" s="8" t="n">
-        <v>0.6818000000000001</v>
+        <v>-0.8634000000000001</v>
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BALIKESİR</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M201" s="6" t="inlineStr"/>
@@ -9238,42 +9234,44 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>86.3</v>
+        <v>10.49</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>-0.048</v>
-      </c>
-      <c r="D202" s="5" t="n">
-        <v>13280000</v>
+        <v>0.09960000000000001</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>16120000</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>0.653</v>
+        <v>0.9556</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>64.23</v>
-      </c>
-      <c r="G202" s="2" t="inlineStr"/>
+        <v>67.11</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>7.13</v>
+      </c>
       <c r="H202" s="3" t="n">
         <v>1.16</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-0.0231</v>
+        <v>0.2011</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>-0.0625</v>
+        <v>0.6818000000000001</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr"/>
@@ -9281,42 +9279,42 @@
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>OSMEN</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="B203" s="7" t="n">
-        <v>7.9</v>
+        <v>86.3</v>
       </c>
       <c r="C203" s="8" t="n">
-        <v>0.0154</v>
+        <v>-0.048</v>
       </c>
       <c r="D203" s="9" t="n">
-        <v>3990000</v>
+        <v>13280000</v>
       </c>
       <c r="E203" s="8" t="n">
-        <v>0.4147</v>
+        <v>0.653</v>
       </c>
       <c r="F203" s="7" t="n">
-        <v>57.26</v>
-      </c>
-      <c r="G203" s="7" t="n">
-        <v>26.28</v>
-      </c>
+        <v>64.23</v>
+      </c>
+      <c r="G203" s="6" t="inlineStr"/>
       <c r="H203" s="7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="I203" s="8" t="n">
-        <v>0.0508</v>
-      </c>
-      <c r="J203" s="6" t="inlineStr"/>
+        <v>-0.0231</v>
+      </c>
+      <c r="J203" s="8" t="n">
+        <v>-0.0625</v>
+      </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M203" s="6" t="inlineStr"/>
@@ -9324,44 +9322,42 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>TLMAN</t>
+          <t>OSMEN</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>99.3</v>
+        <v>7.9</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>0.0398</v>
+        <v>0.0154</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>139580</v>
+        <v>3990000</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>0.4279</v>
+        <v>0.4147</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>62.98</v>
+        <v>57.26</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>38.58</v>
+        <v>26.28</v>
       </c>
       <c r="H204" s="3" t="n">
         <v>1.17</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="J204" s="4" t="n">
-        <v>-6.6864</v>
-      </c>
+        <v>0.0508</v>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr"/>
@@ -9369,115 +9365,117 @@
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>BASCM</t>
+          <t>TLMAN</t>
         </is>
       </c>
       <c r="B205" s="7" t="n">
-        <v>13.9</v>
+        <v>99.3</v>
       </c>
       <c r="C205" s="8" t="n">
-        <v>0.0051</v>
+        <v>0.0398</v>
       </c>
       <c r="D205" s="9" t="n">
-        <v>93000</v>
+        <v>139580</v>
       </c>
       <c r="E205" s="8" t="n">
-        <v>0.1204</v>
+        <v>0.4279</v>
       </c>
       <c r="F205" s="7" t="n">
-        <v>46.35</v>
+        <v>62.98</v>
       </c>
       <c r="G205" s="7" t="n">
-        <v>23.4</v>
+        <v>38.58</v>
       </c>
       <c r="H205" s="7" t="n">
         <v>1.17</v>
       </c>
       <c r="I205" s="8" t="n">
-        <v>0.0579</v>
-      </c>
-      <c r="J205" s="6" t="inlineStr"/>
+        <v>0.0354</v>
+      </c>
+      <c r="J205" s="8" t="n">
+        <v>-6.6864</v>
+      </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
-        </is>
-      </c>
-      <c r="L205" s="6" t="inlineStr"/>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L205" s="6" t="inlineStr">
+        <is>
+          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
+        </is>
+      </c>
       <c r="M205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>POLHO</t>
+          <t>BASCM</t>
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>21</v>
+        <v>13.9</v>
       </c>
       <c r="C206" s="4" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>5290000</v>
+        <v>93000</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>0.2918</v>
+        <v>0.1204</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="G206" s="2" t="inlineStr"/>
+        <v>46.35</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>23.4</v>
+      </c>
       <c r="H206" s="3" t="n">
         <v>1.17</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>-0.0693</v>
-      </c>
-      <c r="J206" s="4" t="n">
-        <v>-9.6821</v>
-      </c>
+        <v>0.0579</v>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L206" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
-        </is>
-      </c>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr"/>
       <c r="M206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="B207" s="7" t="n">
-        <v>45.38</v>
+        <v>21</v>
       </c>
       <c r="C207" s="8" t="n">
-        <v>-0.0139</v>
+        <v>0</v>
       </c>
       <c r="D207" s="9" t="n">
-        <v>442990</v>
+        <v>5290000</v>
       </c>
       <c r="E207" s="8" t="n">
-        <v>0.2133</v>
+        <v>0.2918</v>
       </c>
       <c r="F207" s="7" t="n">
-        <v>55.85</v>
+        <v>47.83</v>
       </c>
       <c r="G207" s="6" t="inlineStr"/>
       <c r="H207" s="7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I207" s="8" t="n">
-        <v>-0.0635</v>
+        <v>-0.0693</v>
       </c>
       <c r="J207" s="8" t="n">
-        <v>-0.0447</v>
+        <v>-9.6821</v>
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
@@ -9486,7 +9484,7 @@
       </c>
       <c r="L207" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M207" s="6" t="inlineStr"/>
@@ -9494,42 +9492,42 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>EGSER</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>3.26</v>
+        <v>45.38</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>0.0252</v>
+        <v>-0.0139</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>5570000</v>
+        <v>442990</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>0.3306</v>
+        <v>0.2133</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>71.48</v>
+        <v>55.85</v>
       </c>
       <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="3" t="n">
         <v>1.18</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>-0.4584</v>
+        <v>-0.0635</v>
       </c>
       <c r="J208" s="4" t="n">
-        <v>-0.3601</v>
+        <v>-0.0447</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr"/>
@@ -9537,42 +9535,42 @@
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>EGSER</t>
         </is>
       </c>
       <c r="B209" s="7" t="n">
-        <v>91.7</v>
+        <v>3.26</v>
       </c>
       <c r="C209" s="8" t="n">
-        <v>0.0438</v>
+        <v>0.0252</v>
       </c>
       <c r="D209" s="9" t="n">
-        <v>311540</v>
+        <v>5570000</v>
       </c>
       <c r="E209" s="8" t="n">
-        <v>0.1275</v>
+        <v>0.3306</v>
       </c>
       <c r="F209" s="7" t="n">
-        <v>63.86</v>
+        <v>71.48</v>
       </c>
       <c r="G209" s="6" t="inlineStr"/>
       <c r="H209" s="7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I209" s="8" t="n">
-        <v>-0.0451</v>
+        <v>-0.4584</v>
       </c>
       <c r="J209" s="8" t="n">
-        <v>-1.622</v>
+        <v>-0.3601</v>
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M209" s="6" t="inlineStr"/>
@@ -11080,44 +11078,44 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>259.25</v>
+        <v>11.85</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>-0.0434</v>
+        <v>0.0128</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>26940000</v>
+        <v>3170000</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>0.4677</v>
+        <v>0.3326</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>48.12</v>
+        <v>49.93</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>17.32</v>
+        <v>349.56</v>
       </c>
       <c r="H244" s="3" t="n">
         <v>1.37</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.0044</v>
       </c>
       <c r="J244" s="4" t="n">
-        <v>-0.3668</v>
+        <v>-1.293</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST KOCAELI, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
         </is>
       </c>
       <c r="M244" s="2" t="inlineStr"/>
@@ -11125,44 +11123,42 @@
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>IHLGM</t>
         </is>
       </c>
       <c r="B245" s="7" t="n">
-        <v>11.85</v>
+        <v>2.39</v>
       </c>
       <c r="C245" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.017</v>
       </c>
       <c r="D245" s="9" t="n">
-        <v>3170000</v>
+        <v>72270000</v>
       </c>
       <c r="E245" s="8" t="n">
-        <v>0.3326</v>
+        <v>0.7498999999999999</v>
       </c>
       <c r="F245" s="7" t="n">
-        <v>49.93</v>
+        <v>66.62</v>
       </c>
       <c r="G245" s="7" t="n">
-        <v>349.56</v>
+        <v>3.84</v>
       </c>
       <c r="H245" s="7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I245" s="8" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="J245" s="8" t="n">
-        <v>-1.293</v>
-      </c>
+        <v>0.4857</v>
+      </c>
+      <c r="J245" s="6" t="inlineStr"/>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M245" s="6" t="inlineStr"/>
@@ -11170,42 +11166,44 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>IHLGM</t>
+          <t>ARTMS</t>
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>2.39</v>
+        <v>43.36</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="D246" s="5" t="n">
-        <v>72270000</v>
+        <v>0.0121</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>2010000</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>0.7498999999999999</v>
+        <v>0.2856</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>66.62</v>
+        <v>50.64</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>3.84</v>
+        <v>12.24</v>
       </c>
       <c r="H246" s="3" t="n">
         <v>1.38</v>
       </c>
       <c r="I246" s="4" t="n">
-        <v>0.4857</v>
-      </c>
-      <c r="J246" s="2" t="inlineStr"/>
+        <v>0.121</v>
+      </c>
+      <c r="J246" s="4" t="n">
+        <v>3.3313</v>
+      </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA</t>
         </is>
       </c>
       <c r="M246" s="2" t="inlineStr"/>
@@ -11213,44 +11211,44 @@
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>ARTMS</t>
+          <t>VAKKO</t>
         </is>
       </c>
       <c r="B247" s="7" t="n">
-        <v>43.36</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C247" s="8" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="D247" s="7" t="n">
-        <v>2010000</v>
+        <v>0.0156</v>
+      </c>
+      <c r="D247" s="9" t="n">
+        <v>562970</v>
       </c>
       <c r="E247" s="8" t="n">
-        <v>0.2856</v>
+        <v>0.1504</v>
       </c>
       <c r="F247" s="7" t="n">
-        <v>50.64</v>
+        <v>53.1</v>
       </c>
       <c r="G247" s="7" t="n">
-        <v>12.24</v>
+        <v>237.05</v>
       </c>
       <c r="H247" s="7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I247" s="8" t="n">
-        <v>0.121</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="J247" s="8" t="n">
-        <v>3.3313</v>
+        <v>328.5973</v>
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M247" s="6" t="inlineStr"/>
@@ -11258,44 +11256,44 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>VAKKO</t>
+          <t>LIDFA</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>84.65000000000001</v>
+        <v>3.66</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>0.0156</v>
+        <v>0.0548</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>562970</v>
+        <v>20570000</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>0.1504</v>
+        <v>0.4208</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>53.1</v>
+        <v>57.54</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>237.05</v>
+        <v>4.11</v>
       </c>
       <c r="H248" s="3" t="n">
         <v>1.39</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.4054</v>
       </c>
       <c r="J248" s="4" t="n">
-        <v>328.5973</v>
+        <v>0.2344</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M248" s="2" t="inlineStr"/>
@@ -11303,44 +11301,42 @@
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>LIDFA</t>
+          <t>HRKET</t>
         </is>
       </c>
       <c r="B249" s="7" t="n">
-        <v>3.66</v>
+        <v>80.25</v>
       </c>
       <c r="C249" s="8" t="n">
-        <v>0.0548</v>
+        <v>-0.0177</v>
       </c>
       <c r="D249" s="9" t="n">
-        <v>20570000</v>
+        <v>1910000</v>
       </c>
       <c r="E249" s="8" t="n">
-        <v>0.4208</v>
+        <v>0.2076</v>
       </c>
       <c r="F249" s="7" t="n">
-        <v>57.54</v>
-      </c>
-      <c r="G249" s="7" t="n">
-        <v>4.11</v>
-      </c>
+        <v>74.81999999999999</v>
+      </c>
+      <c r="G249" s="6" t="inlineStr"/>
       <c r="H249" s="7" t="n">
         <v>1.39</v>
       </c>
       <c r="I249" s="8" t="n">
-        <v>0.4054</v>
+        <v>-0.2435</v>
       </c>
       <c r="J249" s="8" t="n">
-        <v>0.2344</v>
+        <v>-16.4677</v>
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M249" s="6" t="inlineStr"/>
@@ -11348,42 +11344,44 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>HRKET</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>80.25</v>
+        <v>694</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>-0.0177</v>
+        <v>0.0154</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>1910000</v>
+        <v>2460000</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>0.2076</v>
+        <v>0.4918</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>74.81999999999999</v>
-      </c>
-      <c r="G250" s="2" t="inlineStr"/>
+        <v>67.15000000000001</v>
+      </c>
+      <c r="G250" s="3" t="n">
+        <v>17.85</v>
+      </c>
       <c r="H250" s="3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I250" s="4" t="n">
-        <v>-0.2435</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J250" s="4" t="n">
-        <v>-16.4677</v>
+        <v>0.4556</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M250" s="2" t="inlineStr"/>
@@ -11391,44 +11389,44 @@
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="B251" s="7" t="n">
-        <v>694</v>
+        <v>15.18</v>
       </c>
       <c r="C251" s="8" t="n">
-        <v>0.0154</v>
+        <v>0.012</v>
       </c>
       <c r="D251" s="9" t="n">
-        <v>2460000</v>
+        <v>4830000</v>
       </c>
       <c r="E251" s="8" t="n">
-        <v>0.4918</v>
+        <v>0.3903</v>
       </c>
       <c r="F251" s="7" t="n">
-        <v>67.15000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="G251" s="7" t="n">
-        <v>17.85</v>
+        <v>53.24</v>
       </c>
       <c r="H251" s="7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I251" s="8" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0293</v>
       </c>
       <c r="J251" s="8" t="n">
-        <v>0.4556</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M251" s="6" t="inlineStr"/>
@@ -11436,44 +11434,44 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>15.18</v>
+        <v>120</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>0.012</v>
+        <v>0.0213</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>4830000</v>
+        <v>4880000</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>0.3903</v>
+        <v>0.2</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>66.75</v>
+        <v>50.03</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>53.24</v>
+        <v>28.03</v>
       </c>
       <c r="H252" s="3" t="n">
         <v>1.41</v>
       </c>
       <c r="I252" s="4" t="n">
-        <v>0.0293</v>
+        <v>0.0566</v>
       </c>
       <c r="J252" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.6039</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M252" s="2" t="inlineStr"/>
@@ -11481,44 +11479,44 @@
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B253" s="7" t="n">
-        <v>120</v>
+        <v>259.25</v>
       </c>
       <c r="C253" s="8" t="n">
-        <v>0.0213</v>
+        <v>-0.0434</v>
       </c>
       <c r="D253" s="9" t="n">
-        <v>4880000</v>
+        <v>26940000</v>
       </c>
       <c r="E253" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4677</v>
       </c>
       <c r="F253" s="7" t="n">
-        <v>50.03</v>
+        <v>48.12</v>
       </c>
       <c r="G253" s="7" t="n">
-        <v>28.03</v>
+        <v>15.39</v>
       </c>
       <c r="H253" s="7" t="n">
         <v>1.41</v>
       </c>
       <c r="I253" s="8" t="n">
-        <v>0.0566</v>
+        <v>0.1021</v>
       </c>
       <c r="J253" s="8" t="n">
-        <v>-0.6039</v>
+        <v>-0.5182</v>
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST KOCAELI, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M253" s="6" t="inlineStr"/>
@@ -16570,40 +16568,44 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MPARK</t>
         </is>
       </c>
       <c r="B370" s="3" t="n">
-        <v>4.16</v>
+        <v>491.5</v>
       </c>
       <c r="C370" s="4" t="n">
-        <v>0.0272</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="D370" s="5" t="n">
-        <v>35640000</v>
+        <v>1000000</v>
       </c>
       <c r="E370" s="4" t="n">
-        <v>0.2704</v>
+        <v>0.4234000000000001</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="G370" s="2" t="inlineStr"/>
+        <v>64.97</v>
+      </c>
+      <c r="G370" s="3" t="n">
+        <v>16.21</v>
+      </c>
       <c r="H370" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="I370" s="4" t="n">
-        <v>-0.0452</v>
-      </c>
-      <c r="J370" s="2" t="inlineStr"/>
+        <v>0.1752</v>
+      </c>
+      <c r="J370" s="4" t="n">
+        <v>0.1408</v>
+      </c>
       <c r="K370" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M370" s="2" t="inlineStr"/>
@@ -16611,42 +16613,40 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="B371" s="7" t="n">
-        <v>41.7</v>
+        <v>4.16</v>
       </c>
       <c r="C371" s="8" t="n">
-        <v>-0.05230000000000001</v>
+        <v>0.0272</v>
       </c>
       <c r="D371" s="9" t="n">
-        <v>1670000</v>
+        <v>35640000</v>
       </c>
       <c r="E371" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.2704</v>
       </c>
       <c r="F371" s="7" t="n">
-        <v>54.5</v>
+        <v>31.3</v>
       </c>
       <c r="G371" s="6" t="inlineStr"/>
       <c r="H371" s="7" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="I371" s="8" t="n">
-        <v>-0.0684</v>
-      </c>
-      <c r="J371" s="8" t="n">
-        <v>-1.9324</v>
-      </c>
+        <v>-0.0452</v>
+      </c>
+      <c r="J371" s="6" t="inlineStr"/>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M371" s="6" t="inlineStr"/>
@@ -16654,42 +16654,42 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>SONME</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B372" s="3" t="n">
-        <v>141.4</v>
+        <v>41.7</v>
       </c>
       <c r="C372" s="4" t="n">
-        <v>0.0209</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="D372" s="5" t="n">
-        <v>51400</v>
+        <v>1670000</v>
       </c>
       <c r="E372" s="4" t="n">
-        <v>0.0789</v>
+        <v>0.1667</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>50.37</v>
+        <v>54.5</v>
       </c>
       <c r="G372" s="2" t="inlineStr"/>
       <c r="H372" s="3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="I372" s="4" t="n">
-        <v>-0.057</v>
+        <v>-0.0684</v>
       </c>
       <c r="J372" s="4" t="n">
-        <v>-22.838</v>
+        <v>-1.9324</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L372" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M372" s="2" t="inlineStr"/>
@@ -16697,44 +16697,42 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>SONME</t>
         </is>
       </c>
       <c r="B373" s="7" t="n">
-        <v>28.12</v>
+        <v>141.4</v>
       </c>
       <c r="C373" s="8" t="n">
-        <v>0.0144</v>
+        <v>0.0209</v>
       </c>
       <c r="D373" s="9" t="n">
-        <v>7560000</v>
+        <v>51400</v>
       </c>
       <c r="E373" s="8" t="n">
-        <v>0.6767</v>
+        <v>0.0789</v>
       </c>
       <c r="F373" s="7" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="G373" s="7" t="n">
-        <v>106.84</v>
-      </c>
+        <v>50.37</v>
+      </c>
+      <c r="G373" s="6" t="inlineStr"/>
       <c r="H373" s="7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="I373" s="8" t="n">
-        <v>0.0294</v>
+        <v>-0.057</v>
       </c>
       <c r="J373" s="8" t="n">
-        <v>-2.2136</v>
+        <v>-22.838</v>
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM TEMETTU, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST BURSA</t>
         </is>
       </c>
       <c r="M373" s="6" t="inlineStr"/>
@@ -16742,42 +16740,44 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B374" s="3" t="n">
-        <v>3.52</v>
+        <v>28.12</v>
       </c>
       <c r="C374" s="4" t="n">
-        <v>0.0173</v>
+        <v>0.0144</v>
       </c>
       <c r="D374" s="5" t="n">
-        <v>363230000</v>
+        <v>7560000</v>
       </c>
       <c r="E374" s="4" t="n">
-        <v>0.6898000000000001</v>
+        <v>0.6767</v>
       </c>
       <c r="F374" s="3" t="n">
-        <v>67.93000000000001</v>
-      </c>
-      <c r="G374" s="2" t="inlineStr"/>
+        <v>51.04</v>
+      </c>
+      <c r="G374" s="3" t="n">
+        <v>106.84</v>
+      </c>
       <c r="H374" s="3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="I374" s="4" t="n">
-        <v>-0.5265</v>
+        <v>0.0294</v>
       </c>
       <c r="J374" s="4" t="n">
-        <v>-6.582100000000001</v>
+        <v>-2.2136</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L374" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM TEMETTU, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M374" s="2" t="inlineStr"/>
@@ -16785,126 +16785,124 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>EKIZ</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B375" s="7" t="n">
-        <v>95</v>
+        <v>3.52</v>
       </c>
       <c r="C375" s="8" t="n">
-        <v>0.0026</v>
+        <v>0.0173</v>
       </c>
       <c r="D375" s="9" t="n">
-        <v>17720</v>
-      </c>
-      <c r="E375" s="6" t="inlineStr"/>
+        <v>363230000</v>
+      </c>
+      <c r="E375" s="8" t="n">
+        <v>0.6898000000000001</v>
+      </c>
       <c r="F375" s="7" t="n">
-        <v>47.66</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="G375" s="6" t="inlineStr"/>
       <c r="H375" s="7" t="n">
         <v>2.46</v>
       </c>
       <c r="I375" s="8" t="n">
-        <v>-0.1797</v>
+        <v>-0.5265</v>
       </c>
       <c r="J375" s="8" t="n">
-        <v>0.9384</v>
+        <v>-6.582100000000001</v>
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L375" s="6" t="inlineStr"/>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
+      <c r="L375" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M375" s="6" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>LMKDC</t>
+          <t>EKIZ</t>
         </is>
       </c>
       <c r="B376" s="3" t="n">
-        <v>36.5</v>
+        <v>95</v>
       </c>
       <c r="C376" s="4" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0026</v>
       </c>
       <c r="D376" s="5" t="n">
-        <v>9930000</v>
-      </c>
-      <c r="E376" s="4" t="n">
-        <v>0.3012</v>
-      </c>
+        <v>17720</v>
+      </c>
+      <c r="E376" s="2" t="inlineStr"/>
       <c r="F376" s="3" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="G376" s="3" t="n">
-        <v>9.66</v>
-      </c>
+        <v>47.66</v>
+      </c>
+      <c r="G376" s="2" t="inlineStr"/>
       <c r="H376" s="3" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="I376" s="4" t="n">
-        <v>0.3184</v>
+        <v>-0.1797</v>
       </c>
       <c r="J376" s="4" t="n">
-        <v>-0.1897</v>
+        <v>0.9384</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
-        </is>
-      </c>
-      <c r="L376" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L376" s="2" t="inlineStr"/>
       <c r="M376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>EGPRO</t>
+          <t>LMKDC</t>
         </is>
       </c>
       <c r="B377" s="7" t="n">
-        <v>40.6</v>
+        <v>36.5</v>
       </c>
       <c r="C377" s="8" t="n">
-        <v>0.011</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="D377" s="9" t="n">
-        <v>3960000</v>
+        <v>9930000</v>
       </c>
       <c r="E377" s="8" t="n">
-        <v>0.1314</v>
+        <v>0.3012</v>
       </c>
       <c r="F377" s="7" t="n">
-        <v>58.35</v>
+        <v>65.42</v>
       </c>
       <c r="G377" s="7" t="n">
-        <v>22.13</v>
+        <v>9.66</v>
       </c>
       <c r="H377" s="7" t="n">
         <v>2.49</v>
       </c>
       <c r="I377" s="8" t="n">
-        <v>0.132</v>
+        <v>0.3184</v>
       </c>
       <c r="J377" s="8" t="n">
-        <v>0.0143</v>
+        <v>-0.1897</v>
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M377" s="6" t="inlineStr"/>
@@ -16912,33 +16910,35 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>RUZYE</t>
+          <t>EGPRO</t>
         </is>
       </c>
       <c r="B378" s="3" t="n">
-        <v>13.61</v>
+        <v>40.6</v>
       </c>
       <c r="C378" s="4" t="n">
-        <v>-0.0258</v>
+        <v>0.011</v>
       </c>
       <c r="D378" s="5" t="n">
-        <v>11150000</v>
+        <v>3960000</v>
       </c>
       <c r="E378" s="4" t="n">
-        <v>0.6456000000000001</v>
+        <v>0.1314</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="G378" s="2" t="inlineStr"/>
+        <v>58.35</v>
+      </c>
+      <c r="G378" s="3" t="n">
+        <v>22.13</v>
+      </c>
       <c r="H378" s="3" t="n">
         <v>2.49</v>
       </c>
       <c r="I378" s="4" t="n">
-        <v>-0.0029</v>
+        <v>0.132</v>
       </c>
       <c r="J378" s="4" t="n">
-        <v>-3.8066</v>
+        <v>0.0143</v>
       </c>
       <c r="K378" s="2" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="L378" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST ANA, BIST KOBİ SANAYİ, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU, BIST İZMİR</t>
         </is>
       </c>
       <c r="M378" s="2" t="inlineStr"/>
@@ -16955,40 +16955,42 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>GLBMD</t>
+          <t>RUZYE</t>
         </is>
       </c>
       <c r="B379" s="7" t="n">
-        <v>12.03</v>
+        <v>13.61</v>
       </c>
       <c r="C379" s="8" t="n">
-        <v>0.0008</v>
+        <v>-0.0258</v>
       </c>
       <c r="D379" s="9" t="n">
-        <v>438170</v>
-      </c>
-      <c r="E379" s="6" t="inlineStr"/>
+        <v>11150000</v>
+      </c>
+      <c r="E379" s="8" t="n">
+        <v>0.6456000000000001</v>
+      </c>
       <c r="F379" s="7" t="n">
-        <v>45.35</v>
+        <v>61.8</v>
       </c>
       <c r="G379" s="6" t="inlineStr"/>
       <c r="H379" s="7" t="n">
         <v>2.49</v>
       </c>
       <c r="I379" s="8" t="n">
-        <v>-0.1323</v>
+        <v>-0.0029</v>
       </c>
       <c r="J379" s="8" t="n">
-        <v>-0.3689</v>
+        <v>-3.8066</v>
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST ANA, BIST KOBİ SANAYİ, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M379" s="6" t="inlineStr"/>
@@ -16996,42 +16998,40 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CEOEM</t>
+          <t>GLBMD</t>
         </is>
       </c>
       <c r="B380" s="3" t="n">
-        <v>24.84</v>
+        <v>12.03</v>
       </c>
       <c r="C380" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0008</v>
       </c>
       <c r="D380" s="5" t="n">
-        <v>2620000</v>
+        <v>438170</v>
       </c>
       <c r="E380" s="2" t="inlineStr"/>
       <c r="F380" s="3" t="n">
-        <v>59.93</v>
-      </c>
-      <c r="G380" s="3" t="n">
-        <v>385.12</v>
-      </c>
+        <v>45.35</v>
+      </c>
+      <c r="G380" s="2" t="inlineStr"/>
       <c r="H380" s="3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="I380" s="4" t="n">
-        <v>0.0073</v>
+        <v>-0.1323</v>
       </c>
       <c r="J380" s="4" t="n">
-        <v>-0.3059</v>
+        <v>-0.3689</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L380" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR</t>
         </is>
       </c>
       <c r="M380" s="2" t="inlineStr"/>
@@ -17039,40 +17039,42 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>SEKUR</t>
+          <t>CEOEM</t>
         </is>
       </c>
       <c r="B381" s="7" t="n">
-        <v>8.029999999999999</v>
+        <v>24.84</v>
       </c>
       <c r="C381" s="8" t="n">
-        <v>-0.0147</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="D381" s="9" t="n">
-        <v>3630000</v>
-      </c>
-      <c r="E381" s="8" t="n">
-        <v>0.2139</v>
-      </c>
+        <v>2620000</v>
+      </c>
+      <c r="E381" s="6" t="inlineStr"/>
       <c r="F381" s="7" t="n">
-        <v>58.05</v>
-      </c>
-      <c r="G381" s="6" t="inlineStr"/>
+        <v>59.93</v>
+      </c>
+      <c r="G381" s="7" t="n">
+        <v>385.12</v>
+      </c>
       <c r="H381" s="7" t="n">
         <v>2.51</v>
       </c>
       <c r="I381" s="8" t="n">
-        <v>-0.0267</v>
-      </c>
-      <c r="J381" s="6" t="inlineStr"/>
+        <v>0.0073</v>
+      </c>
+      <c r="J381" s="8" t="n">
+        <v>-0.3059</v>
+      </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M381" s="6" t="inlineStr"/>
@@ -17080,42 +17082,40 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>KLSER</t>
+          <t>SEKUR</t>
         </is>
       </c>
       <c r="B382" s="3" t="n">
-        <v>29.34</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="C382" s="4" t="n">
-        <v>0.0014</v>
+        <v>-0.0147</v>
       </c>
       <c r="D382" s="5" t="n">
-        <v>2700000</v>
+        <v>3630000</v>
       </c>
       <c r="E382" s="4" t="n">
-        <v>0.2156</v>
+        <v>0.2139</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>69.66</v>
+        <v>58.05</v>
       </c>
       <c r="G382" s="2" t="inlineStr"/>
       <c r="H382" s="3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="I382" s="4" t="n">
-        <v>-0.5177</v>
-      </c>
-      <c r="J382" s="4" t="n">
-        <v>-2.3054</v>
-      </c>
+        <v>-0.0267</v>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
       <c r="K382" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L382" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM</t>
         </is>
       </c>
       <c r="M382" s="2" t="inlineStr"/>
@@ -17123,42 +17123,42 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>CUSAN</t>
+          <t>KLSER</t>
         </is>
       </c>
       <c r="B383" s="7" t="n">
-        <v>26.14</v>
+        <v>29.34</v>
       </c>
       <c r="C383" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0014</v>
       </c>
       <c r="D383" s="9" t="n">
-        <v>751350</v>
+        <v>2700000</v>
       </c>
       <c r="E383" s="8" t="n">
-        <v>0.2596</v>
+        <v>0.2156</v>
       </c>
       <c r="F383" s="7" t="n">
-        <v>58.67</v>
+        <v>69.66</v>
       </c>
       <c r="G383" s="6" t="inlineStr"/>
       <c r="H383" s="7" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="I383" s="8" t="n">
-        <v>-0.6525</v>
+        <v>-0.5177</v>
       </c>
       <c r="J383" s="8" t="n">
-        <v>-2.2369</v>
+        <v>-2.3054</v>
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M383" s="6" t="inlineStr"/>
@@ -17166,44 +17166,42 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>CUSAN</t>
         </is>
       </c>
       <c r="B384" s="3" t="n">
-        <v>37.8</v>
+        <v>26.14</v>
       </c>
       <c r="C384" s="4" t="n">
-        <v>-0.0278</v>
+        <v>0.0348</v>
       </c>
       <c r="D384" s="5" t="n">
-        <v>33210000</v>
+        <v>751350</v>
       </c>
       <c r="E384" s="4" t="n">
-        <v>0.3779</v>
+        <v>0.2596</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="G384" s="3" t="n">
-        <v>15.6</v>
-      </c>
+        <v>58.67</v>
+      </c>
+      <c r="G384" s="2" t="inlineStr"/>
       <c r="H384" s="3" t="n">
         <v>2.53</v>
       </c>
       <c r="I384" s="4" t="n">
-        <v>0.1993</v>
+        <v>-0.6525</v>
       </c>
       <c r="J384" s="4" t="n">
-        <v>0.1229</v>
+        <v>-2.2369</v>
       </c>
       <c r="K384" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L384" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANTALYA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M384" s="2" t="inlineStr"/>
@@ -17211,44 +17209,44 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>SUNTK</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B385" s="7" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="C385" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.0278</v>
       </c>
       <c r="D385" s="9" t="n">
-        <v>1280000</v>
+        <v>33210000</v>
       </c>
       <c r="E385" s="8" t="n">
-        <v>0.2071</v>
+        <v>0.3779</v>
       </c>
       <c r="F385" s="7" t="n">
-        <v>57.73</v>
+        <v>64.88</v>
       </c>
       <c r="G385" s="7" t="n">
-        <v>26.41</v>
+        <v>15.6</v>
       </c>
       <c r="H385" s="7" t="n">
         <v>2.53</v>
       </c>
       <c r="I385" s="8" t="n">
-        <v>0.1095</v>
+        <v>0.1993</v>
       </c>
       <c r="J385" s="8" t="n">
-        <v>-0.2312</v>
+        <v>0.1229</v>
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST İZMİR, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANTALYA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M385" s="6" t="inlineStr"/>
@@ -17256,44 +17254,44 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>MTRKS</t>
+          <t>SUNTK</t>
         </is>
       </c>
       <c r="B386" s="3" t="n">
-        <v>25.14</v>
+        <v>37.7</v>
       </c>
       <c r="C386" s="4" t="n">
-        <v>0.0295</v>
+        <v>0.0016</v>
       </c>
       <c r="D386" s="5" t="n">
-        <v>1410000</v>
+        <v>1280000</v>
       </c>
       <c r="E386" s="4" t="n">
-        <v>0.4186</v>
+        <v>0.2071</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>73.01000000000001</v>
+        <v>57.73</v>
       </c>
       <c r="G386" s="3" t="n">
-        <v>10.53</v>
+        <v>26.41</v>
       </c>
       <c r="H386" s="3" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="I386" s="4" t="n">
-        <v>0.3117</v>
+        <v>0.1095</v>
       </c>
       <c r="J386" s="4" t="n">
-        <v>0.7249</v>
+        <v>-0.2312</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST İZMİR, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M386" s="2" t="inlineStr"/>
@@ -17301,44 +17299,44 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>MTRKS</t>
         </is>
       </c>
       <c r="B387" s="7" t="n">
-        <v>45.66</v>
+        <v>25.14</v>
       </c>
       <c r="C387" s="8" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0295</v>
       </c>
       <c r="D387" s="9" t="n">
-        <v>5510000</v>
+        <v>1410000</v>
       </c>
       <c r="E387" s="8" t="n">
-        <v>0.7259</v>
+        <v>0.4186</v>
       </c>
       <c r="F387" s="7" t="n">
-        <v>60.86</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G387" s="7" t="n">
-        <v>16.66</v>
+        <v>10.53</v>
       </c>
       <c r="H387" s="7" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="I387" s="8" t="n">
-        <v>0.1794</v>
+        <v>0.3117</v>
       </c>
       <c r="J387" s="8" t="n">
-        <v>-0.9131999999999999</v>
+        <v>0.7249</v>
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST 50-30, BIST KATILIM TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M387" s="6" t="inlineStr"/>
@@ -17346,44 +17344,44 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>KLKIM</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B388" s="3" t="n">
-        <v>36.54</v>
+        <v>45.66</v>
       </c>
       <c r="C388" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="D388" s="5" t="n">
-        <v>3690000</v>
+        <v>5510000</v>
       </c>
       <c r="E388" s="4" t="n">
-        <v>0.2637</v>
+        <v>0.7259</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>51.88</v>
+        <v>60.86</v>
       </c>
       <c r="G388" s="3" t="n">
-        <v>15.38</v>
+        <v>16.66</v>
       </c>
       <c r="H388" s="3" t="n">
         <v>2.58</v>
       </c>
       <c r="I388" s="4" t="n">
-        <v>0.2016</v>
+        <v>0.1794</v>
       </c>
       <c r="J388" s="4" t="n">
-        <v>0.5552</v>
+        <v>-0.9131999999999999</v>
       </c>
       <c r="K388" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L388" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST 50-30, BIST KATILIM TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M388" s="2" t="inlineStr"/>
@@ -17391,42 +17389,44 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>TRILC</t>
+          <t>KLKIM</t>
         </is>
       </c>
       <c r="B389" s="7" t="n">
-        <v>4.05</v>
+        <v>36.54</v>
       </c>
       <c r="C389" s="8" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0345</v>
       </c>
       <c r="D389" s="9" t="n">
-        <v>105210000</v>
+        <v>3690000</v>
       </c>
       <c r="E389" s="8" t="n">
-        <v>0.6164999999999999</v>
+        <v>0.2637</v>
       </c>
       <c r="F389" s="7" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="G389" s="6" t="inlineStr"/>
+        <v>51.88</v>
+      </c>
+      <c r="G389" s="7" t="n">
+        <v>15.38</v>
+      </c>
       <c r="H389" s="7" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="I389" s="8" t="n">
-        <v>-0.3168</v>
+        <v>0.2016</v>
       </c>
       <c r="J389" s="8" t="n">
-        <v>-2.0753</v>
+        <v>0.5552</v>
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M389" s="6" t="inlineStr"/>
@@ -17434,42 +17434,42 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>TRILC</t>
         </is>
       </c>
       <c r="B390" s="3" t="n">
-        <v>138.9</v>
+        <v>4.05</v>
       </c>
       <c r="C390" s="4" t="n">
-        <v>0.0381</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="D390" s="5" t="n">
-        <v>713840</v>
+        <v>105210000</v>
       </c>
       <c r="E390" s="4" t="n">
-        <v>0.5015999999999999</v>
+        <v>0.6164999999999999</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>72.86</v>
+        <v>84.38</v>
       </c>
       <c r="G390" s="2" t="inlineStr"/>
       <c r="H390" s="3" t="n">
         <v>2.59</v>
       </c>
       <c r="I390" s="4" t="n">
-        <v>-0.1212</v>
+        <v>-0.3168</v>
       </c>
       <c r="J390" s="4" t="n">
-        <v>0.7595999999999999</v>
+        <v>-2.0753</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L390" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST DENİZLİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M390" s="2" t="inlineStr"/>
@@ -17477,42 +17477,42 @@
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B391" s="7" t="n">
-        <v>40.74</v>
+        <v>138.9</v>
       </c>
       <c r="C391" s="8" t="n">
-        <v>0.0221</v>
+        <v>0.0381</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>887910</v>
+        <v>713840</v>
       </c>
       <c r="E391" s="8" t="n">
-        <v>0.328</v>
+        <v>0.5015999999999999</v>
       </c>
       <c r="F391" s="7" t="n">
-        <v>63.71</v>
-      </c>
-      <c r="G391" s="7" t="n">
-        <v>258.5</v>
-      </c>
+        <v>72.86</v>
+      </c>
+      <c r="G391" s="6" t="inlineStr"/>
       <c r="H391" s="7" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="I391" s="8" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="J391" s="6" t="inlineStr"/>
+        <v>-0.1212</v>
+      </c>
+      <c r="J391" s="8" t="n">
+        <v>0.7595999999999999</v>
+      </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST DENİZLİ</t>
         </is>
       </c>
       <c r="M391" s="6" t="inlineStr"/>
@@ -17520,44 +17520,42 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>ICBCT</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B392" s="3" t="n">
-        <v>17.22</v>
+        <v>40.74</v>
       </c>
       <c r="C392" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0221</v>
       </c>
       <c r="D392" s="5" t="n">
-        <v>2480000</v>
+        <v>887910</v>
       </c>
       <c r="E392" s="4" t="n">
-        <v>0.0716</v>
+        <v>0.328</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>71.20999999999999</v>
+        <v>63.71</v>
       </c>
       <c r="G392" s="3" t="n">
-        <v>10.88</v>
+        <v>258.5</v>
       </c>
       <c r="H392" s="3" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="I392" s="4" t="n">
-        <v>0.2722</v>
-      </c>
-      <c r="J392" s="4" t="n">
-        <v>0.0377</v>
-      </c>
+        <v>0.0114</v>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
       <c r="K392" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L392" s="2" t="inlineStr">
         <is>
-          <t>BIST BANKA, BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M392" s="2" t="inlineStr"/>
@@ -17565,42 +17563,44 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>VSNMD</t>
+          <t>ICBCT</t>
         </is>
       </c>
       <c r="B393" s="7" t="n">
-        <v>88.34999999999999</v>
+        <v>17.22</v>
       </c>
       <c r="C393" s="8" t="n">
-        <v>0.0155</v>
+        <v>0.01</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>2600000</v>
+        <v>2480000</v>
       </c>
       <c r="E393" s="8" t="n">
-        <v>0.2051</v>
+        <v>0.0716</v>
       </c>
       <c r="F393" s="7" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="G393" s="6" t="inlineStr"/>
+        <v>71.20999999999999</v>
+      </c>
+      <c r="G393" s="7" t="n">
+        <v>10.88</v>
+      </c>
       <c r="H393" s="7" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="I393" s="8" t="n">
-        <v>-0.0218</v>
+        <v>0.2722</v>
       </c>
       <c r="J393" s="8" t="n">
-        <v>-2.8047</v>
+        <v>0.0377</v>
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST HALKA ARZ, BIST ANA, ADANA</t>
+          <t>BIST BANKA, BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M393" s="6" t="inlineStr"/>
@@ -17608,42 +17608,42 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>EGEEN</t>
+          <t>VSNMD</t>
         </is>
       </c>
       <c r="B394" s="3" t="n">
-        <v>6562.5</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="C394" s="4" t="n">
-        <v>0.0218</v>
+        <v>0.0155</v>
       </c>
       <c r="D394" s="5" t="n">
-        <v>18310</v>
+        <v>2600000</v>
       </c>
       <c r="E394" s="4" t="n">
-        <v>0.3637</v>
+        <v>0.2051</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>58.02</v>
+        <v>54.3</v>
       </c>
       <c r="G394" s="2" t="inlineStr"/>
       <c r="H394" s="3" t="n">
         <v>2.64</v>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-0.0145</v>
+        <v>-0.0218</v>
       </c>
       <c r="J394" s="4" t="n">
-        <v>-13.2704</v>
+        <v>-2.8047</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST HALKA ARZ, BIST ANA, ADANA</t>
         </is>
       </c>
       <c r="M394" s="2" t="inlineStr"/>
@@ -17651,44 +17651,42 @@
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>EBEBK</t>
+          <t>EGEEN</t>
         </is>
       </c>
       <c r="B395" s="7" t="n">
-        <v>75.90000000000001</v>
+        <v>6562.5</v>
       </c>
       <c r="C395" s="8" t="n">
-        <v>0.0086</v>
+        <v>0.0218</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>637970</v>
+        <v>18310</v>
       </c>
       <c r="E395" s="8" t="n">
-        <v>0.2408</v>
+        <v>0.3637</v>
       </c>
       <c r="F395" s="7" t="n">
-        <v>69.16</v>
-      </c>
-      <c r="G395" s="7" t="n">
-        <v>191.91</v>
-      </c>
+        <v>58.02</v>
+      </c>
+      <c r="G395" s="6" t="inlineStr"/>
       <c r="H395" s="7" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I395" s="8" t="n">
-        <v>0.0154</v>
+        <v>-0.0145</v>
       </c>
       <c r="J395" s="8" t="n">
-        <v>-0.8693000000000001</v>
+        <v>-13.2704</v>
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST İZMİR</t>
         </is>
       </c>
       <c r="M395" s="6" t="inlineStr"/>
@@ -17696,40 +17694,44 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>DESPC</t>
+          <t>EBEBK</t>
         </is>
       </c>
       <c r="B396" s="3" t="n">
-        <v>46.82</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="C396" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="D396" s="5" t="n">
-        <v>1310000</v>
-      </c>
-      <c r="E396" s="2" t="inlineStr"/>
+        <v>637970</v>
+      </c>
+      <c r="E396" s="4" t="n">
+        <v>0.2408</v>
+      </c>
       <c r="F396" s="3" t="n">
-        <v>65.68000000000001</v>
-      </c>
-      <c r="G396" s="2" t="inlineStr"/>
+        <v>69.16</v>
+      </c>
+      <c r="G396" s="3" t="n">
+        <v>191.91</v>
+      </c>
       <c r="H396" s="3" t="n">
         <v>2.66</v>
       </c>
       <c r="I396" s="4" t="n">
-        <v>-0.1176</v>
+        <v>0.0154</v>
       </c>
       <c r="J396" s="4" t="n">
-        <v>-19.3798</v>
+        <v>-0.8693000000000001</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L396" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M396" s="2" t="inlineStr"/>
@@ -17737,128 +17739,124 @@
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
         <is>
-          <t>KLNMA</t>
+          <t>DESPC</t>
         </is>
       </c>
       <c r="B397" s="7" t="n">
-        <v>9.6</v>
+        <v>46.82</v>
       </c>
       <c r="C397" s="8" t="n">
-        <v>0.0042</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>276040</v>
-      </c>
-      <c r="E397" s="8" t="n">
-        <v>0.0092</v>
-      </c>
+        <v>1310000</v>
+      </c>
+      <c r="E397" s="6" t="inlineStr"/>
       <c r="F397" s="7" t="n">
-        <v>46.17</v>
-      </c>
-      <c r="G397" s="7" t="n">
-        <v>13.19</v>
-      </c>
+        <v>65.68000000000001</v>
+      </c>
+      <c r="G397" s="6" t="inlineStr"/>
       <c r="H397" s="7" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="I397" s="8" t="n">
-        <v>0.3408</v>
+        <v>-0.1176</v>
       </c>
       <c r="J397" s="8" t="n">
-        <v>-0.0144</v>
+        <v>-19.3798</v>
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L397" s="6" t="inlineStr"/>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
+      <c r="L397" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M397" s="6" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>TTRAK</t>
+          <t>KLNMA</t>
         </is>
       </c>
       <c r="B398" s="3" t="n">
-        <v>457.75</v>
+        <v>9.6</v>
       </c>
       <c r="C398" s="4" t="n">
-        <v>0.0144</v>
+        <v>0.0042</v>
       </c>
       <c r="D398" s="5" t="n">
-        <v>164780</v>
+        <v>276040</v>
       </c>
       <c r="E398" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0092</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="G398" s="2" t="inlineStr"/>
+        <v>46.17</v>
+      </c>
+      <c r="G398" s="3" t="n">
+        <v>13.19</v>
+      </c>
       <c r="H398" s="3" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-0.0716</v>
+        <v>0.3408</v>
       </c>
       <c r="J398" s="4" t="n">
-        <v>-1.7616</v>
+        <v>-0.0144</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L398" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST ANKARA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L398" s="2" t="inlineStr"/>
       <c r="M398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>TTRAK</t>
         </is>
       </c>
       <c r="B399" s="7" t="n">
-        <v>491.5</v>
+        <v>457.75</v>
       </c>
       <c r="C399" s="8" t="n">
-        <v>0.08259999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>1000000</v>
+        <v>164780</v>
       </c>
       <c r="E399" s="8" t="n">
-        <v>0.4234000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="F399" s="7" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="G399" s="7" t="n">
-        <v>17.73</v>
-      </c>
+        <v>45.61</v>
+      </c>
+      <c r="G399" s="6" t="inlineStr"/>
       <c r="H399" s="7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I399" s="8" t="n">
-        <v>0.1843</v>
+        <v>-0.0716</v>
       </c>
       <c r="J399" s="8" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-1.7616</v>
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST ANKARA</t>
         </is>
       </c>
       <c r="M399" s="6" t="inlineStr"/>
@@ -25904,21 +25902,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>183.8</v>
+        <v>20.7</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>6730000</v>
+        <v>59910000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>64.56</v>
+        <v>43.43</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25926,12 +25924,12 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25939,34 +25937,40 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>42.28</v>
+        <v>2.72</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>5650000</v>
-      </c>
-      <c r="E587" s="6" t="inlineStr"/>
+        <v>30640000</v>
+      </c>
+      <c r="E587" s="8" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F587" s="7" t="n">
-        <v>59</v>
+        <v>45.04</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
+      <c r="I587" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J587" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25974,40 +25978,34 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>146.2</v>
+        <v>2.9</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0054</v>
+        <v>0.0175</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="E588" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>187970000</v>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>50.15</v>
+        <v>54.16</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J588" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -26015,42 +26013,34 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>18.2</v>
+        <v>18.88</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0111</v>
+        <v>0.0043</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>14620000</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>77480000</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>60.45</v>
-      </c>
-      <c r="G589" s="7" t="n">
-        <v>172.02</v>
-      </c>
+        <v>57.12</v>
+      </c>
+      <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J589" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I589" s="6" t="inlineStr"/>
+      <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26058,42 +26048,34 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>36.08</v>
+        <v>42.28</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0244</v>
+        <v>-0.0075</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>6890000</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.3528</v>
-      </c>
+        <v>5650000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>46.26</v>
-      </c>
-      <c r="G590" s="3" t="n">
-        <v>14.26</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>0.1029</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-1.4864</v>
-      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26101,40 +26083,34 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>7.14</v>
+        <v>14.8</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.09960000000000001</v>
+        <v>0.0379</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>114930000</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>32030000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>58.68</v>
+        <v>61.05</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26142,40 +26118,34 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>2.72</v>
+        <v>35.5</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="D592" s="5" t="n">
-        <v>30640000</v>
-      </c>
-      <c r="E592" s="4" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>0.0553</v>
+      </c>
+      <c r="D592" s="3" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>45.04</v>
+        <v>61.24</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="4" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J592" s="4" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26183,40 +26153,34 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>19.98</v>
+        <v>183.8</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0924</v>
+        <v>0.0349</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>792640</v>
-      </c>
-      <c r="E593" s="8" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>6730000</v>
+      </c>
+      <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>67.12</v>
+        <v>64.56</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="8" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J593" s="8" t="n">
-        <v>0.3246</v>
-      </c>
+      <c r="I593" s="6" t="inlineStr"/>
+      <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26224,73 +26188,75 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>30.42</v>
+        <v>8.16</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.0242</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>15210000</v>
+        <v>791430</v>
       </c>
       <c r="E594" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.95</v>
       </c>
       <c r="F594" s="3" t="n">
-        <v>57.13</v>
+        <v>51.35</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
-      <c r="I594" s="2" t="inlineStr"/>
-      <c r="J594" s="2" t="inlineStr"/>
+      <c r="I594" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J594" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr"/>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>35.5</v>
+        <v>84</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="D595" s="7" t="n">
-        <v>4150000</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
+        <v>0.0633</v>
+      </c>
+      <c r="D595" s="9" t="n">
+        <v>52620</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F595" s="7" t="n">
-        <v>61.24</v>
+        <v>51.11</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
+      <c r="I595" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J595" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr"/>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
@@ -26327,34 +26293,42 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>48.4</v>
+        <v>36.08</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.1</v>
+        <v>0.0244</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>12860000</v>
-      </c>
-      <c r="E597" s="6" t="inlineStr"/>
+        <v>6890000</v>
+      </c>
+      <c r="E597" s="8" t="n">
+        <v>0.3528</v>
+      </c>
       <c r="F597" s="7" t="n">
-        <v>69.08</v>
-      </c>
-      <c r="G597" s="6" t="inlineStr"/>
+        <v>46.26</v>
+      </c>
+      <c r="G597" s="7" t="n">
+        <v>14.26</v>
+      </c>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>-1.4864</v>
+      </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26362,23 +26336,21 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>6.89</v>
+        <v>30.06</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.09369999999999999</v>
+        <v>0.0437</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>50430000</v>
-      </c>
-      <c r="E598" s="4" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>23750000</v>
+      </c>
+      <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>87.08</v>
+        <v>68.52</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26386,12 +26358,12 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26399,71 +26371,79 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>8.16</v>
+        <v>30.42</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.09970000000000001</v>
+        <v>0.0242</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>791430</v>
+        <v>15210000</v>
       </c>
       <c r="E599" s="8" t="n">
-        <v>0.95</v>
+        <v>0.2667</v>
       </c>
       <c r="F599" s="7" t="n">
-        <v>51.35</v>
+        <v>57.13</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J599" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I599" s="6" t="inlineStr"/>
+      <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L599" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L599" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>2.9</v>
+        <v>18.2</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0175</v>
+        <v>0.0111</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>187970000</v>
-      </c>
-      <c r="E600" s="2" t="inlineStr"/>
+        <v>14620000</v>
+      </c>
+      <c r="E600" s="4" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F600" s="3" t="n">
-        <v>54.16</v>
-      </c>
-      <c r="G600" s="2" t="inlineStr"/>
+        <v>60.45</v>
+      </c>
+      <c r="G600" s="3" t="n">
+        <v>172.02</v>
+      </c>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="2" t="inlineStr"/>
-      <c r="J600" s="2" t="inlineStr"/>
+      <c r="I600" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J600" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26471,60 +26451,62 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>84</v>
+        <v>7.14</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0.0633</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>52620</v>
+        <v>114930000</v>
       </c>
       <c r="E601" s="8" t="n">
-        <v>0.58</v>
+        <v>0.1672</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>51.11</v>
+        <v>58.68</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="8" t="n">
-        <v>-9.409700000000001</v>
+        <v>-5.3262</v>
       </c>
       <c r="J601" s="8" t="n">
-        <v>-4.155</v>
+        <v>-4.2562</v>
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>244.9</v>
+        <v>197</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0179</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>8620</v>
-      </c>
-      <c r="E602" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>15180000</v>
+      </c>
+      <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>45.77</v>
+        <v>49.17</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
@@ -26532,30 +26514,36 @@
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>197</v>
+        <v>6.89</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>15180000</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>50430000</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>49.17</v>
+        <v>87.08</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26563,12 +26551,12 @@
       <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26576,21 +26564,21 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>18.88</v>
+        <v>82</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0043</v>
+        <v>0.0142</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>77480000</v>
+        <v>204340</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>57.12</v>
+        <v>11.68</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26598,51 +26586,43 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>68.75</v>
+        <v>48.4</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0223</v>
+        <v>0.1</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>830940</v>
-      </c>
-      <c r="E605" s="8" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>12860000</v>
+      </c>
+      <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>64.02</v>
+        <v>69.08</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="6" t="inlineStr"/>
-      <c r="J605" s="8" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26650,21 +26630,21 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>30.06</v>
+        <v>18.2</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0437</v>
+        <v>0.0406</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>23750000</v>
+        <v>68110000</v>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>68.52</v>
+        <v>57.11</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26672,12 +26652,12 @@
       <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26685,34 +26665,40 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>14.8</v>
+        <v>19.98</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0924</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>32030000</v>
-      </c>
-      <c r="E607" s="6" t="inlineStr"/>
+        <v>792640</v>
+      </c>
+      <c r="E607" s="8" t="n">
+        <v>0.9869</v>
+      </c>
       <c r="F607" s="7" t="n">
-        <v>61.05</v>
+        <v>67.12</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
+      <c r="I607" s="8" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J607" s="8" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -26720,56 +26706,50 @@
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B608" s="3" t="n">
-        <v>20.7</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="C608" s="4" t="n">
-        <v>0.09519999999999999</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="D608" s="5" t="n">
-        <v>59910000</v>
+        <v>10010000</v>
       </c>
       <c r="E608" s="2" t="inlineStr"/>
       <c r="F608" s="3" t="n">
-        <v>43.43</v>
+        <v>49.94</v>
       </c>
       <c r="G608" s="2" t="inlineStr"/>
       <c r="H608" s="2" t="inlineStr"/>
       <c r="I608" s="2" t="inlineStr"/>
       <c r="J608" s="2" t="inlineStr"/>
-      <c r="K608" s="2" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L608" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="K608" s="2" t="inlineStr"/>
+      <c r="L608" s="2" t="inlineStr"/>
       <c r="M608" s="2" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B609" s="7" t="n">
-        <v>18.2</v>
+        <v>244.9</v>
       </c>
       <c r="C609" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0179</v>
       </c>
       <c r="D609" s="9" t="n">
-        <v>68110000</v>
-      </c>
-      <c r="E609" s="6" t="inlineStr"/>
+        <v>8620</v>
+      </c>
+      <c r="E609" s="8" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F609" s="7" t="n">
-        <v>57.11</v>
+        <v>45.77</v>
       </c>
       <c r="G609" s="6" t="inlineStr"/>
       <c r="H609" s="6" t="inlineStr"/>
@@ -26777,72 +26757,90 @@
       <c r="J609" s="6" t="inlineStr"/>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L609" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L609" s="6" t="inlineStr"/>
       <c r="M609" s="6" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B610" s="3" t="n">
-        <v>82</v>
+        <v>146.2</v>
       </c>
       <c r="C610" s="4" t="n">
-        <v>0.0142</v>
+        <v>-0.0054</v>
       </c>
       <c r="D610" s="5" t="n">
-        <v>204340</v>
-      </c>
-      <c r="E610" s="2" t="inlineStr"/>
+        <v>1290000</v>
+      </c>
+      <c r="E610" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F610" s="3" t="n">
-        <v>11.68</v>
+        <v>50.15</v>
       </c>
       <c r="G610" s="2" t="inlineStr"/>
       <c r="H610" s="2" t="inlineStr"/>
-      <c r="I610" s="2" t="inlineStr"/>
-      <c r="J610" s="2" t="inlineStr"/>
+      <c r="I610" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J610" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L610" s="2" t="inlineStr"/>
+          <t>Perakende satış</t>
+        </is>
+      </c>
+      <c r="L610" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+        </is>
+      </c>
       <c r="M610" s="2" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B611" s="7" t="n">
-        <v>81.65000000000001</v>
+        <v>68.75</v>
       </c>
       <c r="C611" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0223</v>
       </c>
       <c r="D611" s="9" t="n">
-        <v>10010000</v>
-      </c>
-      <c r="E611" s="6" t="inlineStr"/>
+        <v>830940</v>
+      </c>
+      <c r="E611" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F611" s="7" t="n">
-        <v>49.94</v>
+        <v>64.02</v>
       </c>
       <c r="G611" s="6" t="inlineStr"/>
       <c r="H611" s="6" t="inlineStr"/>
       <c r="I611" s="6" t="inlineStr"/>
-      <c r="J611" s="6" t="inlineStr"/>
-      <c r="K611" s="6" t="inlineStr"/>
-      <c r="L611" s="6" t="inlineStr"/>
+      <c r="J611" s="8" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="K611" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
+      <c r="L611" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M611" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26867,7 +26865,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>07.05.2026 15:30</t>
+          <t>07.05.2026 16:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-07.xlsx
+++ b/data/bist_screener_2026-05-07.xlsx
@@ -25902,21 +25902,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>20.7</v>
+        <v>48.4</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.09519999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>59910000</v>
+        <v>12860000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>43.43</v>
+        <v>69.08</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25924,12 +25924,12 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25937,40 +25937,40 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>2.72</v>
+        <v>146.2</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0074</v>
+        <v>-0.0054</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>30640000</v>
+        <v>1290000</v>
       </c>
       <c r="E587" s="8" t="n">
-        <v>0.7119</v>
+        <v>0.1071</v>
       </c>
       <c r="F587" s="7" t="n">
-        <v>45.04</v>
+        <v>50.15</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
       <c r="I587" s="8" t="n">
-        <v>-191.6342</v>
+        <v>-3.6635</v>
       </c>
       <c r="J587" s="8" t="n">
-        <v>-0.8093</v>
+        <v>-0.4897</v>
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25978,34 +25978,38 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>2.9</v>
+        <v>68.75</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0175</v>
+        <v>0.0223</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>187970000</v>
-      </c>
-      <c r="E588" s="2" t="inlineStr"/>
+        <v>830940</v>
+      </c>
+      <c r="E588" s="4" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F588" s="3" t="n">
-        <v>54.16</v>
+        <v>64.02</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
       <c r="I588" s="2" t="inlineStr"/>
-      <c r="J588" s="2" t="inlineStr"/>
+      <c r="J588" s="4" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -26013,21 +26017,21 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>18.88</v>
+        <v>6.16</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>77480000</v>
+        <v>6910000</v>
       </c>
       <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>57.12</v>
+        <v>61.49</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -26035,69 +26039,67 @@
       <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L589" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L589" s="6" t="inlineStr"/>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>42.28</v>
+        <v>8.16</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0075</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>5650000</v>
-      </c>
-      <c r="E590" s="2" t="inlineStr"/>
+        <v>791430</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F590" s="3" t="n">
-        <v>59</v>
+        <v>51.35</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J590" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>14.8</v>
+        <v>183.8</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0349</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>32030000</v>
+        <v>6730000</v>
       </c>
       <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>61.05</v>
+        <v>64.56</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
@@ -26105,12 +26107,12 @@
       <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26118,34 +26120,40 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>35.5</v>
+        <v>2.72</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="D592" s="3" t="n">
-        <v>4150000</v>
-      </c>
-      <c r="E592" s="2" t="inlineStr"/>
+        <v>0.0074</v>
+      </c>
+      <c r="D592" s="5" t="n">
+        <v>30640000</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F592" s="3" t="n">
-        <v>61.24</v>
+        <v>45.04</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="2" t="inlineStr"/>
-      <c r="J592" s="2" t="inlineStr"/>
+      <c r="I592" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J592" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26153,21 +26161,21 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>183.8</v>
+        <v>18.88</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0043</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>6730000</v>
+        <v>77480000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>64.56</v>
+        <v>57.12</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26180,7 +26188,7 @@
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26188,72 +26196,64 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>8.16</v>
+        <v>20.7</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.09970000000000001</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>791430</v>
-      </c>
-      <c r="E594" s="4" t="n">
-        <v>0.95</v>
-      </c>
+        <v>59910000</v>
+      </c>
+      <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>51.35</v>
+        <v>43.43</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
-      <c r="I594" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J594" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I594" s="2" t="inlineStr"/>
+      <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0633</v>
+        <v>0.0142</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>52620</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.58</v>
-      </c>
+        <v>204340</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>51.11</v>
+        <v>11.68</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J595" s="8" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I595" s="6" t="inlineStr"/>
+      <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -26262,21 +26262,21 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>6.16</v>
+        <v>30.06</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0</v>
+        <v>0.0437</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>6910000</v>
+        <v>23750000</v>
       </c>
       <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>61.49</v>
+        <v>68.52</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
@@ -26284,51 +26284,47 @@
       <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr"/>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
+      <c r="L596" s="2" t="inlineStr">
+        <is>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>36.08</v>
+        <v>14.8</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0244</v>
+        <v>0.0379</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>6890000</v>
-      </c>
-      <c r="E597" s="8" t="n">
-        <v>0.3528</v>
-      </c>
+        <v>32030000</v>
+      </c>
+      <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>46.26</v>
-      </c>
-      <c r="G597" s="7" t="n">
-        <v>14.26</v>
-      </c>
+        <v>61.05</v>
+      </c>
+      <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="8" t="n">
-        <v>0.1029</v>
-      </c>
-      <c r="J597" s="8" t="n">
-        <v>-1.4864</v>
-      </c>
+      <c r="I597" s="6" t="inlineStr"/>
+      <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26336,21 +26332,21 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>30.06</v>
+        <v>18.2</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.0437</v>
+        <v>0.0406</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>23750000</v>
+        <v>68110000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>68.52</v>
+        <v>57.11</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26358,12 +26354,12 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26371,23 +26367,21 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>30.42</v>
+        <v>42.28</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0242</v>
+        <v>-0.0075</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>15210000</v>
-      </c>
-      <c r="E599" s="8" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>5650000</v>
+      </c>
+      <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>57.13</v>
+        <v>59</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26395,12 +26389,12 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26408,83 +26402,61 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>18.2</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0111</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>14620000</v>
-      </c>
-      <c r="E600" s="4" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>10010000</v>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>60.45</v>
-      </c>
-      <c r="G600" s="3" t="n">
-        <v>172.02</v>
-      </c>
+        <v>49.94</v>
+      </c>
+      <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J600" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
-      <c r="K600" s="2" t="inlineStr">
-        <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
-        </is>
-      </c>
+      <c r="I600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr"/>
+      <c r="K600" s="2" t="inlineStr"/>
+      <c r="L600" s="2" t="inlineStr"/>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>7.14</v>
+        <v>35.5</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.09960000000000001</v>
-      </c>
-      <c r="D601" s="9" t="n">
-        <v>114930000</v>
-      </c>
-      <c r="E601" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>0.0553</v>
+      </c>
+      <c r="D601" s="7" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="E601" s="6" t="inlineStr"/>
       <c r="F601" s="7" t="n">
-        <v>58.68</v>
+        <v>61.24</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J601" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I601" s="6" t="inlineStr"/>
+      <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26492,63 +26464,69 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0633</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>15180000</v>
-      </c>
-      <c r="E602" s="2" t="inlineStr"/>
+        <v>52620</v>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F602" s="3" t="n">
-        <v>49.17</v>
+        <v>51.11</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="2" t="inlineStr"/>
-      <c r="J602" s="2" t="inlineStr"/>
+      <c r="I602" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J602" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr"/>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>6.89</v>
+        <v>7.14</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.09369999999999999</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>50430000</v>
+        <v>114930000</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.1672</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>87.08</v>
+        <v>58.68</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J603" s="8" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26556,7 +26534,7 @@
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26564,21 +26542,23 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>82</v>
+        <v>244.9</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0179</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>204340</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>8620</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F604" s="3" t="n">
-        <v>11.68</v>
+        <v>45.77</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26586,7 +26566,7 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr"/>
@@ -26595,21 +26575,23 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>48.4</v>
+        <v>30.42</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.1</v>
+        <v>0.0242</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>12860000</v>
-      </c>
-      <c r="E605" s="6" t="inlineStr"/>
+        <v>15210000</v>
+      </c>
+      <c r="E605" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F605" s="7" t="n">
-        <v>69.08</v>
+        <v>57.13</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
@@ -26617,12 +26599,12 @@
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26630,34 +26612,42 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0406</v>
+        <v>0.0111</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>68110000</v>
-      </c>
-      <c r="E606" s="2" t="inlineStr"/>
+        <v>14620000</v>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F606" s="3" t="n">
-        <v>57.11</v>
-      </c>
-      <c r="G606" s="2" t="inlineStr"/>
+        <v>60.45</v>
+      </c>
+      <c r="G606" s="3" t="n">
+        <v>172.02</v>
+      </c>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="2" t="inlineStr"/>
-      <c r="J606" s="2" t="inlineStr"/>
+      <c r="I606" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J606" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26706,50 +26696,64 @@
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="B608" s="3" t="n">
-        <v>81.65000000000001</v>
+        <v>36.08</v>
       </c>
       <c r="C608" s="4" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0244</v>
       </c>
       <c r="D608" s="5" t="n">
-        <v>10010000</v>
-      </c>
-      <c r="E608" s="2" t="inlineStr"/>
+        <v>6890000</v>
+      </c>
+      <c r="E608" s="4" t="n">
+        <v>0.3528</v>
+      </c>
       <c r="F608" s="3" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="G608" s="2" t="inlineStr"/>
+        <v>46.26</v>
+      </c>
+      <c r="G608" s="3" t="n">
+        <v>14.26</v>
+      </c>
       <c r="H608" s="2" t="inlineStr"/>
-      <c r="I608" s="2" t="inlineStr"/>
-      <c r="J608" s="2" t="inlineStr"/>
-      <c r="K608" s="2" t="inlineStr"/>
-      <c r="L608" s="2" t="inlineStr"/>
+      <c r="I608" s="4" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="J608" s="4" t="n">
+        <v>-1.4864</v>
+      </c>
+      <c r="K608" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
+      <c r="L608" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+        </is>
+      </c>
       <c r="M608" s="2" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B609" s="7" t="n">
-        <v>244.9</v>
+        <v>197</v>
       </c>
       <c r="C609" s="8" t="n">
-        <v>0.0179</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D609" s="9" t="n">
-        <v>8620</v>
-      </c>
-      <c r="E609" s="8" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>15180000</v>
+      </c>
+      <c r="E609" s="6" t="inlineStr"/>
       <c r="F609" s="7" t="n">
-        <v>45.77</v>
+        <v>49.17</v>
       </c>
       <c r="G609" s="6" t="inlineStr"/>
       <c r="H609" s="6" t="inlineStr"/>
@@ -26757,49 +26761,47 @@
       <c r="J609" s="6" t="inlineStr"/>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L609" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L609" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M609" s="6" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B610" s="3" t="n">
-        <v>146.2</v>
+        <v>2.9</v>
       </c>
       <c r="C610" s="4" t="n">
-        <v>-0.0054</v>
+        <v>0.0175</v>
       </c>
       <c r="D610" s="5" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="E610" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>187970000</v>
+      </c>
+      <c r="E610" s="2" t="inlineStr"/>
       <c r="F610" s="3" t="n">
-        <v>50.15</v>
+        <v>54.16</v>
       </c>
       <c r="G610" s="2" t="inlineStr"/>
       <c r="H610" s="2" t="inlineStr"/>
-      <c r="I610" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J610" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I610" s="2" t="inlineStr"/>
+      <c r="J610" s="2" t="inlineStr"/>
       <c r="K610" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L610" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M610" s="2" t="inlineStr"/>
@@ -26807,38 +26809,36 @@
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B611" s="7" t="n">
-        <v>68.75</v>
+        <v>6.89</v>
       </c>
       <c r="C611" s="8" t="n">
-        <v>0.0223</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="D611" s="9" t="n">
-        <v>830940</v>
+        <v>50430000</v>
       </c>
       <c r="E611" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.8667</v>
       </c>
       <c r="F611" s="7" t="n">
-        <v>64.02</v>
+        <v>87.08</v>
       </c>
       <c r="G611" s="6" t="inlineStr"/>
       <c r="H611" s="6" t="inlineStr"/>
       <c r="I611" s="6" t="inlineStr"/>
-      <c r="J611" s="8" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J611" s="6" t="inlineStr"/>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M611" s="6" t="inlineStr"/>
@@ -26865,7 +26865,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>07.05.2026 16:30</t>
+          <t>07.05.2026 17:15</t>
         </is>
       </c>
     </row>
